--- a/自动算分.xlsx
+++ b/自动算分.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15789" uniqueCount="2829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15841" uniqueCount="2829">
   <si>
     <t>名次</t>
   </si>
@@ -13005,7 +13005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" s="3" customFormat="1" spans="1:9">
+    <row r="123" s="3" customFormat="1" hidden="1" spans="1:9">
       <c r="A123" s="1">
         <v>1</v>
       </c>
@@ -13561,7 +13561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" hidden="1" spans="1:9">
       <c r="A143" s="8">
         <v>1</v>
       </c>
@@ -16287,7 +16287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="243" s="3" customFormat="1" spans="1:9">
+    <row r="243" s="3" customFormat="1" hidden="1" spans="1:9">
       <c r="A243" s="1">
         <v>2</v>
       </c>
@@ -16507,7 +16507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" s="3" customFormat="1" spans="1:9">
+    <row r="251" s="3" customFormat="1" hidden="1" spans="1:9">
       <c r="A251" s="1">
         <v>2</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" s="3" customFormat="1" spans="1:9">
+    <row r="252" s="3" customFormat="1" hidden="1" spans="1:9">
       <c r="A252" s="1">
         <v>3</v>
       </c>
@@ -17584,7 +17584,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
+    <row r="290" hidden="1" spans="1:9">
       <c r="A290" s="8">
         <v>1</v>
       </c>
@@ -19389,7 +19389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="357" spans="1:9">
+    <row r="357" hidden="1" spans="1:9">
       <c r="A357" s="8">
         <v>3</v>
       </c>
@@ -21491,7 +21491,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="433" spans="1:9">
+    <row r="433" hidden="1" spans="1:9">
       <c r="A433" s="8">
         <v>1</v>
       </c>
@@ -21708,7 +21708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="441" spans="1:9">
+    <row r="441" hidden="1" spans="1:9">
       <c r="A441" s="8">
         <v>1</v>
       </c>
@@ -26520,7 +26520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="621" spans="1:9">
+    <row r="621" hidden="1" spans="1:9">
       <c r="A621" s="8">
         <v>3</v>
       </c>
@@ -26676,7 +26676,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="627" spans="1:9">
+    <row r="627" hidden="1" spans="1:9">
       <c r="A627" s="8">
         <v>1</v>
       </c>
@@ -29193,7 +29193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="720" spans="1:9">
+    <row r="720" hidden="1" spans="1:9">
       <c r="A720" s="8">
         <v>1</v>
       </c>
@@ -29219,7 +29219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="721" spans="1:9">
+    <row r="721" hidden="1" spans="1:9">
       <c r="A721" s="8">
         <v>2</v>
       </c>
@@ -31056,7 +31056,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="789" spans="1:9">
+    <row r="789" hidden="1" spans="1:9">
       <c r="A789" s="8">
         <v>2</v>
       </c>
@@ -32692,7 +32692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="851" spans="1:9">
+    <row r="851" hidden="1" spans="1:9">
       <c r="A851" s="8">
         <v>1</v>
       </c>
@@ -32973,7 +32973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="861" spans="1:9">
+    <row r="861" hidden="1" spans="1:9">
       <c r="A861" s="8">
         <v>3</v>
       </c>
@@ -33144,7 +33144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="867" spans="1:9">
+    <row r="867" hidden="1" spans="1:9">
       <c r="A867" s="8">
         <v>1</v>
       </c>
@@ -33358,7 +33358,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="875" hidden="1" spans="1:7">
+    <row r="875" spans="1:9">
       <c r="A875" s="8">
         <v>1</v>
       </c>
@@ -33380,8 +33380,11 @@
       <c r="G875" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="876" hidden="1" spans="1:7">
+      <c r="I875" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="876" spans="1:9">
       <c r="A876" s="8">
         <v>2</v>
       </c>
@@ -33403,8 +33406,11 @@
       <c r="G876" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="877" hidden="1" spans="1:7">
+      <c r="I876" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="877" spans="1:9">
       <c r="A877" s="8">
         <v>3</v>
       </c>
@@ -33426,8 +33432,11 @@
       <c r="G877" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="878" hidden="1" spans="1:7">
+      <c r="I877" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="878" spans="1:9">
       <c r="A878" s="8">
         <v>4</v>
       </c>
@@ -33449,8 +33458,11 @@
       <c r="G878" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="879" hidden="1" spans="1:7">
+      <c r="I878" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="879" spans="1:9">
       <c r="A879" s="8">
         <v>5</v>
       </c>
@@ -33472,8 +33484,11 @@
       <c r="G879" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="880" hidden="1" spans="1:7">
+      <c r="I879" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="880" spans="1:9">
       <c r="A880" s="8">
         <v>6</v>
       </c>
@@ -33495,8 +33510,11 @@
       <c r="G880" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="881" hidden="1" spans="1:7">
+      <c r="I880" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="881" spans="1:9">
       <c r="A881" s="8">
         <v>7</v>
       </c>
@@ -33518,8 +33536,11 @@
       <c r="G881" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="882" hidden="1" spans="1:7">
+      <c r="I881" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="882" spans="1:9">
       <c r="A882" s="8">
         <v>8</v>
       </c>
@@ -33541,8 +33562,11 @@
       <c r="G882" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="883" hidden="1" spans="1:7">
+      <c r="I882" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="883" spans="1:9">
       <c r="A883" s="8">
         <v>9</v>
       </c>
@@ -33564,8 +33588,11 @@
       <c r="G883" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="884" hidden="1" spans="1:7">
+      <c r="I883" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="884" spans="1:9">
       <c r="A884" s="8">
         <v>10</v>
       </c>
@@ -33587,8 +33614,11 @@
       <c r="G884" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="885" hidden="1" spans="1:7">
+      <c r="I884" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="885" spans="1:9">
       <c r="A885" s="8">
         <v>11</v>
       </c>
@@ -33610,8 +33640,11 @@
       <c r="G885" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="886" hidden="1" spans="1:7">
+      <c r="I885" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="886" spans="1:9">
       <c r="A886" s="8">
         <v>12</v>
       </c>
@@ -33633,8 +33666,11 @@
       <c r="G886" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="887" hidden="1" spans="1:7">
+      <c r="I886" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="887" spans="1:9">
       <c r="A887" s="8">
         <v>1</v>
       </c>
@@ -33656,8 +33692,11 @@
       <c r="G887" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="888" hidden="1" spans="1:7">
+      <c r="I887" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="888" spans="1:9">
       <c r="A888" s="8">
         <v>2</v>
       </c>
@@ -33679,8 +33718,11 @@
       <c r="G888" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="889" hidden="1" spans="1:7">
+      <c r="I888" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="889" spans="1:9">
       <c r="A889" s="8">
         <v>3</v>
       </c>
@@ -33702,8 +33744,11 @@
       <c r="G889" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="890" hidden="1" spans="1:7">
+      <c r="I889" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="890" spans="1:9">
       <c r="A890" s="8">
         <v>4</v>
       </c>
@@ -33725,8 +33770,11 @@
       <c r="G890" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="891" hidden="1" spans="1:7">
+      <c r="I890" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="891" spans="1:9">
       <c r="A891" s="8">
         <v>5</v>
       </c>
@@ -33748,8 +33796,11 @@
       <c r="G891" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="892" hidden="1" spans="1:7">
+      <c r="I891" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="892" spans="1:9">
       <c r="A892" s="8">
         <v>6</v>
       </c>
@@ -33771,8 +33822,11 @@
       <c r="G892" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="893" hidden="1" spans="1:7">
+      <c r="I892" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="893" spans="1:9">
       <c r="A893" s="8">
         <v>7</v>
       </c>
@@ -33794,8 +33848,11 @@
       <c r="G893" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="894" hidden="1" spans="1:7">
+      <c r="I893" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="894" spans="1:9">
       <c r="A894" s="8">
         <v>8</v>
       </c>
@@ -33817,8 +33874,11 @@
       <c r="G894" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="895" hidden="1" spans="1:7">
+      <c r="I894" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="895" spans="1:9">
       <c r="A895" s="8">
         <v>9</v>
       </c>
@@ -33840,8 +33900,11 @@
       <c r="G895" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="896" hidden="1" spans="1:7">
+      <c r="I895" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="896" spans="1:9">
       <c r="A896" s="8">
         <v>10</v>
       </c>
@@ -33863,8 +33926,11 @@
       <c r="G896" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="897" hidden="1" spans="1:7">
+      <c r="I896" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="897" spans="1:9">
       <c r="A897" s="8">
         <v>11</v>
       </c>
@@ -33886,8 +33952,11 @@
       <c r="G897" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="898" hidden="1" spans="1:7">
+      <c r="I897" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="898" spans="1:9">
       <c r="A898" s="8">
         <v>12</v>
       </c>
@@ -33909,8 +33978,11 @@
       <c r="G898" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="899" hidden="1" spans="1:7">
+      <c r="I898" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="899" spans="1:9">
       <c r="A899" s="8">
         <v>13</v>
       </c>
@@ -33932,8 +34004,11 @@
       <c r="G899" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="900" hidden="1" spans="1:7">
+      <c r="I899" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="900" spans="1:9">
       <c r="A900" s="8">
         <v>14</v>
       </c>
@@ -33955,8 +34030,11 @@
       <c r="G900" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="901" hidden="1" spans="1:7">
+      <c r="I900" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="901" spans="1:9">
       <c r="A901" s="8">
         <v>15</v>
       </c>
@@ -33978,8 +34056,11 @@
       <c r="G901" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="902" hidden="1" spans="1:7">
+      <c r="I901" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="902" spans="1:9">
       <c r="A902" s="8">
         <v>1</v>
       </c>
@@ -34001,8 +34082,11 @@
       <c r="G902" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="903" hidden="1" spans="1:7">
+      <c r="I902" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="903" spans="1:9">
       <c r="A903" s="8">
         <v>2</v>
       </c>
@@ -34024,8 +34108,11 @@
       <c r="G903" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="904" hidden="1" spans="1:7">
+      <c r="I903" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="904" spans="1:9">
       <c r="A904" s="8">
         <v>3</v>
       </c>
@@ -34047,8 +34134,11 @@
       <c r="G904" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="905" hidden="1" spans="1:7">
+      <c r="I904" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="905" spans="1:9">
       <c r="A905" s="8">
         <v>4</v>
       </c>
@@ -34070,8 +34160,11 @@
       <c r="G905" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="906" hidden="1" spans="1:7">
+      <c r="I905" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="906" spans="1:9">
       <c r="A906" s="8">
         <v>5</v>
       </c>
@@ -34093,8 +34186,11 @@
       <c r="G906" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="907" hidden="1" spans="1:7">
+      <c r="I906" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="907" spans="1:9">
       <c r="A907" s="8">
         <v>6</v>
       </c>
@@ -34116,8 +34212,11 @@
       <c r="G907" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="908" hidden="1" spans="1:7">
+      <c r="I907" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="908" spans="1:9">
       <c r="A908" s="8">
         <v>7</v>
       </c>
@@ -34139,8 +34238,11 @@
       <c r="G908" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="909" hidden="1" spans="1:7">
+      <c r="I908" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="909" spans="1:9">
       <c r="A909" s="8">
         <v>8</v>
       </c>
@@ -34162,8 +34264,11 @@
       <c r="G909" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="910" hidden="1" spans="1:7">
+      <c r="I909" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="910" spans="1:9">
       <c r="A910" s="8">
         <v>1</v>
       </c>
@@ -34185,8 +34290,11 @@
       <c r="G910" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="911" hidden="1" spans="1:7">
+      <c r="I910" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="911" spans="1:9">
       <c r="A911" s="8">
         <v>2</v>
       </c>
@@ -34208,8 +34316,11 @@
       <c r="G911" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="912" hidden="1" spans="1:7">
+      <c r="I911" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="912" spans="1:9">
       <c r="A912" s="8">
         <v>3</v>
       </c>
@@ -34231,8 +34342,11 @@
       <c r="G912" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="913" hidden="1" spans="1:7">
+      <c r="I912" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="913" spans="1:9">
       <c r="A913" s="8">
         <v>4</v>
       </c>
@@ -34254,8 +34368,11 @@
       <c r="G913" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="914" hidden="1" spans="1:7">
+      <c r="I913" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="914" spans="1:9">
       <c r="A914" s="8">
         <v>5</v>
       </c>
@@ -34277,8 +34394,11 @@
       <c r="G914" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="915" hidden="1" spans="1:7">
+      <c r="I914" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="915" spans="1:9">
       <c r="A915" s="8">
         <v>1</v>
       </c>
@@ -34300,8 +34420,11 @@
       <c r="G915" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="916" hidden="1" spans="1:7">
+      <c r="I915" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="916" spans="1:9">
       <c r="A916" s="8">
         <v>2</v>
       </c>
@@ -34323,8 +34446,11 @@
       <c r="G916" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="917" hidden="1" spans="1:7">
+      <c r="I916" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="917" spans="1:9">
       <c r="A917" s="8">
         <v>3</v>
       </c>
@@ -34346,8 +34472,11 @@
       <c r="G917" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="918" hidden="1" spans="1:7">
+      <c r="I917" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="918" spans="1:9">
       <c r="A918" s="8">
         <v>4</v>
       </c>
@@ -34369,8 +34498,11 @@
       <c r="G918" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="919" hidden="1" spans="1:7">
+      <c r="I918" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="919" spans="1:9">
       <c r="A919" s="8">
         <v>1</v>
       </c>
@@ -34392,8 +34524,11 @@
       <c r="G919" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="920" hidden="1" spans="1:7">
+      <c r="I919" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="920" spans="1:9">
       <c r="A920" s="8">
         <v>2</v>
       </c>
@@ -34415,8 +34550,11 @@
       <c r="G920" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="921" spans="1:7">
+      <c r="I920" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="921" spans="1:9">
       <c r="A921" s="8">
         <v>3</v>
       </c>
@@ -34438,8 +34576,11 @@
       <c r="G921" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="922" hidden="1" spans="1:7">
+      <c r="I921" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="922" spans="1:9">
       <c r="A922" s="8">
         <v>4</v>
       </c>
@@ -34461,8 +34602,11 @@
       <c r="G922" s="8">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="923" hidden="1" spans="1:7">
+      <c r="I922" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="923" spans="1:9">
       <c r="A923" s="8">
         <v>4</v>
       </c>
@@ -34484,8 +34628,11 @@
       <c r="G923" s="8">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="924" hidden="1" spans="1:7">
+      <c r="I923" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="924" spans="1:9">
       <c r="A924" s="8">
         <v>6</v>
       </c>
@@ -34507,8 +34654,11 @@
       <c r="G924" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="925" hidden="1" spans="1:7">
+      <c r="I924" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="925" spans="1:9">
       <c r="A925" s="8">
         <v>7</v>
       </c>
@@ -34530,8 +34680,11 @@
       <c r="G925" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="926" hidden="1" spans="1:7">
+      <c r="I925" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="926" spans="1:9">
       <c r="A926" s="8">
         <v>8</v>
       </c>
@@ -34553,45 +34706,14 @@
       <c r="G926" s="8">
         <v>1</v>
       </c>
+      <c r="I926" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I926" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="1"/>
-        <filter val="2"/>
-        <filter val="3"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="女子100米"/>
-        <filter val="女子400米"/>
-        <filter val="男子400米"/>
-        <filter val="女子跳高"/>
-        <filter val="男子异程接力"/>
-        <filter val="异程接力"/>
-        <filter val="混合4x100米接力"/>
-        <filter val="男子4x400米接力"/>
-        <filter val="男子4x100米接力"/>
-        <filter val="女子4x400米接力"/>
-        <filter val="女子4x100米接力"/>
-        <filter val="女子三级跳远"/>
-        <filter val="男子跳远团体总排名"/>
-        <filter val="女子400米栏"/>
-        <filter val="男子110米栏"/>
-        <filter val="男子400米栏"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="广东"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="8">
-      <filters blank="1">
-        <filter val="决赛"/>
-      </filters>
+      <filters blank="1"/>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/自动算分.xlsx
+++ b/自动算分.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15841" uniqueCount="2829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15842" uniqueCount="2829">
   <si>
     <t>名次</t>
   </si>
@@ -4636,28 +4636,28 @@
     <t>男子4x400米接力</t>
   </si>
   <si>
+    <t>3:09.63 (0.188s)</t>
+  </si>
+  <si>
+    <t>3:12.57 (0.141s)</t>
+  </si>
+  <si>
+    <t>3:14.42 (0.206s)</t>
+  </si>
+  <si>
+    <t>3:14.85 (0.204s)</t>
+  </si>
+  <si>
+    <t>3:14.89 (0.211s)</t>
+  </si>
+  <si>
+    <t>3:15.33 (0.224s)</t>
+  </si>
+  <si>
+    <t>3:16.11 (0.183s)</t>
+  </si>
+  <si>
     <t>3:08.64 (0.227s)</t>
-  </si>
-  <si>
-    <t>3:09.63 (0.188s)</t>
-  </si>
-  <si>
-    <t>3:12.57 (0.141s)</t>
-  </si>
-  <si>
-    <t>3:14.42 (0.206s)</t>
-  </si>
-  <si>
-    <t>3:14.85 (0.204s)</t>
-  </si>
-  <si>
-    <t>3:14.89 (0.211s)</t>
-  </si>
-  <si>
-    <t>3:15.33 (0.224s)</t>
-  </si>
-  <si>
-    <t>3:16.11 (0.183s)</t>
   </si>
   <si>
     <t>女子4x400米接力</t>
@@ -9278,6 +9278,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -9623,7 +9626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:I926"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -9665,7 +9668,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="2" s="3" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -9694,7 +9697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="3" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -9721,7 +9724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="4" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -9750,7 +9753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="5" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -9777,7 +9780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="6" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -9804,7 +9807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="7" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -9833,7 +9836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="8" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -9862,7 +9865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="9" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -9891,7 +9894,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="10" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -9920,7 +9923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="11" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -9947,7 +9950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="12" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -9974,7 +9977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="13" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -10003,7 +10006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="14" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -10030,7 +10033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="15" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -10059,7 +10062,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="16" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -10086,7 +10089,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="17" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -10113,7 +10116,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="18" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -10142,7 +10145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="19" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -10171,7 +10174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="20" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -10198,7 +10201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="21" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -10225,7 +10228,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="22" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -10254,7 +10257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="23" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -10281,7 +10284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="24" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -10308,7 +10311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="25" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -10335,7 +10338,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="26" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -10362,7 +10365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="27" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -10389,7 +10392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="28" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -10416,7 +10419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="29" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -10443,7 +10446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="30" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
@@ -10468,7 +10471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="31" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A31" s="5" t="s">
         <v>83</v>
       </c>
@@ -10493,7 +10496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="32" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A32" s="5">
         <v>1</v>
       </c>
@@ -10522,7 +10525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="33" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A33" s="5">
         <v>2</v>
       </c>
@@ -10549,7 +10552,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="34" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A34" s="5">
         <v>3</v>
       </c>
@@ -10578,7 +10581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="35" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A35" s="5">
         <v>4</v>
       </c>
@@ -10607,7 +10610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="36" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A36" s="5">
         <v>5</v>
       </c>
@@ -10634,7 +10637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="37" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A37" s="5">
         <v>6</v>
       </c>
@@ -10663,7 +10666,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="38" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A38" s="5">
         <v>7</v>
       </c>
@@ -10692,7 +10695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="39" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A39" s="5">
         <v>8</v>
       </c>
@@ -10719,7 +10722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="40" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A40" s="5">
         <v>9</v>
       </c>
@@ -10746,7 +10749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="41" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A41" s="5">
         <v>10</v>
       </c>
@@ -10773,7 +10776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="42" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A42" s="5">
         <v>11</v>
       </c>
@@ -10802,7 +10805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="43" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A43" s="5">
         <v>12</v>
       </c>
@@ -10829,7 +10832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="44" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A44" s="5">
         <v>13</v>
       </c>
@@ -10858,7 +10861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="45" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A45" s="5">
         <v>14</v>
       </c>
@@ -10885,7 +10888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="46" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A46" s="5">
         <v>15</v>
       </c>
@@ -10912,7 +10915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="47" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A47" s="5">
         <v>16</v>
       </c>
@@ -10941,7 +10944,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="48" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A48" s="5">
         <v>17</v>
       </c>
@@ -10968,7 +10971,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="49" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A49" s="5">
         <v>18</v>
       </c>
@@ -10997,7 +11000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="50" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A50" s="5">
         <v>19</v>
       </c>
@@ -11024,7 +11027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="51" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A51" s="5">
         <v>20</v>
       </c>
@@ -11051,7 +11054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="52" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A52" s="5">
         <v>21</v>
       </c>
@@ -11078,7 +11081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="53" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A53" s="5">
         <v>22</v>
       </c>
@@ -11105,7 +11108,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="54" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A54" s="5">
         <v>23</v>
       </c>
@@ -11132,7 +11135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="55" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A55" s="5">
         <v>24</v>
       </c>
@@ -11159,7 +11162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="56" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A56" s="5">
         <v>25</v>
       </c>
@@ -11186,7 +11189,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="57" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A57" s="5">
         <v>26</v>
       </c>
@@ -11213,7 +11216,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="58" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A58" s="5">
         <v>27</v>
       </c>
@@ -11240,7 +11243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="59" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A59" s="5">
         <v>28</v>
       </c>
@@ -11267,7 +11270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="60" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A60" s="5">
         <v>29</v>
       </c>
@@ -11294,7 +11297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="61" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A61" s="5">
         <v>30</v>
       </c>
@@ -11321,7 +11324,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="62" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A62" s="5">
         <v>31</v>
       </c>
@@ -11350,7 +11353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="63" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A63" s="5">
         <v>32</v>
       </c>
@@ -11379,7 +11382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="64" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A64" s="5">
         <v>33</v>
       </c>
@@ -11406,7 +11409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="65" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A65" s="5">
         <v>34</v>
       </c>
@@ -11433,7 +11436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="66" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A66" s="5" t="s">
         <v>83</v>
       </c>
@@ -11460,7 +11463,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="67" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A67" s="5" t="s">
         <v>83</v>
       </c>
@@ -11487,7 +11490,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="68" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A68" s="5" t="s">
         <v>83</v>
       </c>
@@ -11514,7 +11517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="69" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A69" s="5" t="s">
         <v>83</v>
       </c>
@@ -11541,7 +11544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="70" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A70" s="5" t="s">
         <v>83</v>
       </c>
@@ -11568,7 +11571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="71" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A71" s="5" t="s">
         <v>83</v>
       </c>
@@ -11595,7 +11598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" s="7" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="72" s="7" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A72" s="5" t="s">
         <v>83</v>
       </c>
@@ -11622,7 +11625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" s="3" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="73" s="3" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A73" s="13">
         <v>1</v>
       </c>
@@ -11651,7 +11654,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" s="3" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="74" s="3" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A74" s="13">
         <v>2</v>
       </c>
@@ -11680,7 +11683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" s="3" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="75" s="3" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A75" s="13">
         <v>3</v>
       </c>
@@ -11709,7 +11712,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" s="3" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="76" s="3" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A76" s="13">
         <v>4</v>
       </c>
@@ -11738,7 +11741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="77" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A77" s="5">
         <v>5</v>
       </c>
@@ -11765,7 +11768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="78" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A78" s="5">
         <v>6</v>
       </c>
@@ -11794,7 +11797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="79" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A79" s="5">
         <v>7</v>
       </c>
@@ -11823,7 +11826,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="80" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A80" s="5">
         <v>8</v>
       </c>
@@ -11852,7 +11855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="81" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A81" s="5">
         <v>9</v>
       </c>
@@ -11879,7 +11882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="82" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A82" s="5">
         <v>10</v>
       </c>
@@ -11908,7 +11911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="83" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A83" s="5">
         <v>11</v>
       </c>
@@ -11935,7 +11938,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="84" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A84" s="5">
         <v>12</v>
       </c>
@@ -11962,7 +11965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" customFormat="1" ht="18.5" hidden="1" customHeight="1" spans="1:9">
+    <row r="85" customFormat="1" ht="18.5" customHeight="1" spans="1:9">
       <c r="A85" s="5">
         <v>13</v>
       </c>
@@ -11991,7 +11994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:9">
+    <row r="86" spans="1:9">
       <c r="A86" s="8">
         <v>1</v>
       </c>
@@ -12017,7 +12020,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:9">
+    <row r="87" spans="1:9">
       <c r="A87" s="8">
         <v>2</v>
       </c>
@@ -12046,7 +12049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:9">
+    <row r="88" spans="1:9">
       <c r="A88" s="8">
         <v>3</v>
       </c>
@@ -12075,7 +12078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:9">
+    <row r="89" spans="1:9">
       <c r="A89" s="8">
         <v>4</v>
       </c>
@@ -12104,7 +12107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:9">
+    <row r="90" spans="1:9">
       <c r="A90" s="8">
         <v>5</v>
       </c>
@@ -12130,7 +12133,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:9">
+    <row r="91" spans="1:9">
       <c r="A91" s="8">
         <v>6</v>
       </c>
@@ -12156,7 +12159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:9">
+    <row r="92" spans="1:9">
       <c r="A92" s="8">
         <v>7</v>
       </c>
@@ -12182,7 +12185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:9">
+    <row r="93" spans="1:9">
       <c r="A93" s="8" t="s">
         <v>83</v>
       </c>
@@ -12208,7 +12211,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:9">
+    <row r="94" spans="1:9">
       <c r="A94" s="8">
         <v>1</v>
       </c>
@@ -12237,7 +12240,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:9">
+    <row r="95" spans="1:9">
       <c r="A95" s="8">
         <v>2</v>
       </c>
@@ -12266,7 +12269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:9">
+    <row r="96" spans="1:9">
       <c r="A96" s="8">
         <v>3</v>
       </c>
@@ -12292,7 +12295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:9">
+    <row r="97" spans="1:9">
       <c r="A97" s="8">
         <v>4</v>
       </c>
@@ -12318,7 +12321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:9">
+    <row r="98" spans="1:9">
       <c r="A98" s="8">
         <v>5</v>
       </c>
@@ -12344,7 +12347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:9">
+    <row r="99" spans="1:9">
       <c r="A99" s="8">
         <v>6</v>
       </c>
@@ -12371,7 +12374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="100" s="3" customFormat="1" spans="1:9">
       <c r="A100" s="1">
         <v>1</v>
       </c>
@@ -12400,7 +12403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:9">
+    <row r="101" spans="1:9">
       <c r="A101" s="8">
         <v>2</v>
       </c>
@@ -12429,7 +12432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:9">
+    <row r="102" spans="1:9">
       <c r="A102" s="8">
         <v>3</v>
       </c>
@@ -12455,7 +12458,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:9">
+    <row r="103" spans="1:9">
       <c r="A103" s="8">
         <v>4</v>
       </c>
@@ -12484,7 +12487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:9">
+    <row r="104" spans="1:9">
       <c r="A104" s="8">
         <v>5</v>
       </c>
@@ -12510,7 +12513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:9">
+    <row r="105" spans="1:9">
       <c r="A105" s="8">
         <v>6</v>
       </c>
@@ -12536,7 +12539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:9">
+    <row r="106" spans="1:9">
       <c r="A106" s="8">
         <v>7</v>
       </c>
@@ -12562,7 +12565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:9">
+    <row r="107" spans="1:9">
       <c r="A107" s="8">
         <v>8</v>
       </c>
@@ -12591,7 +12594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:9">
+    <row r="108" spans="1:9">
       <c r="A108" s="8">
         <v>9</v>
       </c>
@@ -12617,7 +12620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:9">
+    <row r="109" spans="1:9">
       <c r="A109" s="8">
         <v>10</v>
       </c>
@@ -12643,7 +12646,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:9">
+    <row r="110" spans="1:9">
       <c r="A110" s="8">
         <v>11</v>
       </c>
@@ -12669,7 +12672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:9">
+    <row r="111" spans="1:9">
       <c r="A111" s="8">
         <v>12</v>
       </c>
@@ -12695,7 +12698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:9">
+    <row r="112" spans="1:9">
       <c r="A112" s="8">
         <v>1</v>
       </c>
@@ -12724,7 +12727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:9">
+    <row r="113" spans="1:9">
       <c r="A113" s="8">
         <v>2</v>
       </c>
@@ -12753,7 +12756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:9">
+    <row r="114" spans="1:9">
       <c r="A114" s="8">
         <v>3</v>
       </c>
@@ -12782,7 +12785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:9">
+    <row r="115" spans="1:9">
       <c r="A115" s="8">
         <v>4</v>
       </c>
@@ -12811,7 +12814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:9">
+    <row r="116" spans="1:9">
       <c r="A116" s="8">
         <v>5</v>
       </c>
@@ -12840,7 +12843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:9">
+    <row r="117" spans="1:9">
       <c r="A117" s="8">
         <v>6</v>
       </c>
@@ -12866,7 +12869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:9">
+    <row r="118" spans="1:9">
       <c r="A118" s="8">
         <v>7</v>
       </c>
@@ -12895,7 +12898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:9">
+    <row r="119" spans="1:9">
       <c r="A119" s="8">
         <v>8</v>
       </c>
@@ -12924,7 +12927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:9">
+    <row r="120" spans="1:9">
       <c r="A120" s="8">
         <v>9</v>
       </c>
@@ -12953,7 +12956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:9">
+    <row r="121" spans="1:9">
       <c r="A121" s="8">
         <v>10</v>
       </c>
@@ -12979,7 +12982,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:9">
+    <row r="122" spans="1:9">
       <c r="A122" s="8">
         <v>11</v>
       </c>
@@ -13005,7 +13008,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="123" s="3" customFormat="1" spans="1:9">
       <c r="A123" s="1">
         <v>1</v>
       </c>
@@ -13034,7 +13037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:9">
+    <row r="124" spans="1:9">
       <c r="A124" s="8">
         <v>2</v>
       </c>
@@ -13060,7 +13063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:9">
+    <row r="125" spans="1:9">
       <c r="A125" s="8">
         <v>3</v>
       </c>
@@ -13089,7 +13092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:9">
+    <row r="126" spans="1:9">
       <c r="A126" s="8">
         <v>4</v>
       </c>
@@ -13118,7 +13121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:9">
+    <row r="127" spans="1:9">
       <c r="A127" s="8">
         <v>5</v>
       </c>
@@ -13147,7 +13150,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:9">
+    <row r="128" spans="1:9">
       <c r="A128" s="8">
         <v>6</v>
       </c>
@@ -13173,7 +13176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:9">
+    <row r="129" spans="1:9">
       <c r="A129" s="8">
         <v>7</v>
       </c>
@@ -13202,7 +13205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:9">
+    <row r="130" spans="1:9">
       <c r="A130" s="8">
         <v>8</v>
       </c>
@@ -13231,7 +13234,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:9">
+    <row r="131" spans="1:9">
       <c r="A131" s="8">
         <v>9</v>
       </c>
@@ -13260,7 +13263,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:9">
+    <row r="132" spans="1:9">
       <c r="A132" s="8">
         <v>10</v>
       </c>
@@ -13289,7 +13292,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:9">
+    <row r="133" spans="1:9">
       <c r="A133" s="8">
         <v>11</v>
       </c>
@@ -13315,7 +13318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:9">
+    <row r="134" spans="1:9">
       <c r="A134" s="8">
         <v>12</v>
       </c>
@@ -13341,7 +13344,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="1:9">
+    <row r="135" spans="1:9">
       <c r="A135" s="8">
         <v>13</v>
       </c>
@@ -13367,7 +13370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:9">
+    <row r="136" spans="1:9">
       <c r="A136" s="8">
         <v>14</v>
       </c>
@@ -13396,7 +13399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="1:9">
+    <row r="137" spans="1:9">
       <c r="A137" s="8">
         <v>15</v>
       </c>
@@ -13425,7 +13428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:9">
+    <row r="138" spans="1:9">
       <c r="A138" s="8">
         <v>16</v>
       </c>
@@ -13454,7 +13457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="1:9">
+    <row r="139" spans="1:9">
       <c r="A139" s="8">
         <v>17</v>
       </c>
@@ -13483,7 +13486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:9">
+    <row r="140" spans="1:9">
       <c r="A140" s="8">
         <v>18</v>
       </c>
@@ -13509,7 +13512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="1:9">
+    <row r="141" spans="1:9">
       <c r="A141" s="8">
         <v>19</v>
       </c>
@@ -13535,7 +13538,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:9">
+    <row r="142" spans="1:9">
       <c r="A142" s="8" t="s">
         <v>83</v>
       </c>
@@ -13561,7 +13564,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="1:9">
+    <row r="143" spans="1:9">
       <c r="A143" s="8">
         <v>1</v>
       </c>
@@ -13590,7 +13593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="1:9">
+    <row r="144" spans="1:9">
       <c r="A144" s="8">
         <v>2</v>
       </c>
@@ -13619,7 +13622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:9">
+    <row r="145" spans="1:9">
       <c r="A145" s="8">
         <v>3</v>
       </c>
@@ -13648,7 +13651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="1:9">
+    <row r="146" spans="1:9">
       <c r="A146" s="8">
         <v>4</v>
       </c>
@@ -13677,7 +13680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="1:9">
+    <row r="147" spans="1:9">
       <c r="A147" s="8">
         <v>5</v>
       </c>
@@ -13706,7 +13709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:9">
+    <row r="148" spans="1:9">
       <c r="A148" s="8">
         <v>6</v>
       </c>
@@ -13735,7 +13738,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:9">
+    <row r="149" spans="1:9">
       <c r="A149" s="8">
         <v>7</v>
       </c>
@@ -13761,7 +13764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:9">
+    <row r="150" spans="1:9">
       <c r="A150" s="8">
         <v>8</v>
       </c>
@@ -13787,7 +13790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:9">
+    <row r="151" spans="1:9">
       <c r="A151" s="8">
         <v>9</v>
       </c>
@@ -13813,7 +13816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" hidden="1" spans="1:9">
+    <row r="152" spans="1:9">
       <c r="A152" s="8">
         <v>10</v>
       </c>
@@ -13842,7 +13845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" hidden="1" spans="1:9">
+    <row r="153" spans="1:9">
       <c r="A153" s="8">
         <v>11</v>
       </c>
@@ -13868,7 +13871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" hidden="1" spans="1:9">
+    <row r="154" spans="1:9">
       <c r="A154" s="8">
         <v>12</v>
       </c>
@@ -13894,7 +13897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" hidden="1" spans="1:9">
+    <row r="155" spans="1:9">
       <c r="A155" s="8">
         <v>13</v>
       </c>
@@ -13920,7 +13923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" hidden="1" spans="1:9">
+    <row r="156" spans="1:9">
       <c r="A156" s="8">
         <v>14</v>
       </c>
@@ -13949,7 +13952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" hidden="1" spans="1:9">
+    <row r="157" spans="1:9">
       <c r="A157" s="8">
         <v>15</v>
       </c>
@@ -13975,7 +13978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" hidden="1" spans="1:9">
+    <row r="158" spans="1:9">
       <c r="A158" s="8">
         <v>16</v>
       </c>
@@ -14004,7 +14007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" hidden="1" spans="1:9">
+    <row r="159" spans="1:9">
       <c r="A159" s="8">
         <v>17</v>
       </c>
@@ -14030,7 +14033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" hidden="1" spans="1:9">
+    <row r="160" spans="1:9">
       <c r="A160" s="8">
         <v>18</v>
       </c>
@@ -14056,7 +14059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" hidden="1" spans="1:9">
+    <row r="161" spans="1:9">
       <c r="A161" s="8" t="s">
         <v>83</v>
       </c>
@@ -14082,7 +14085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="1:9">
+    <row r="162" spans="1:9">
       <c r="A162" s="8" t="s">
         <v>83</v>
       </c>
@@ -14108,7 +14111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:9">
+    <row r="163" spans="1:9">
       <c r="A163" s="8" t="s">
         <v>83</v>
       </c>
@@ -14134,7 +14137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="164" s="3" customFormat="1" spans="1:9">
       <c r="A164" s="1">
         <v>1</v>
       </c>
@@ -14163,7 +14166,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="165" s="3" customFormat="1" spans="1:9">
       <c r="A165" s="1">
         <v>2</v>
       </c>
@@ -14192,7 +14195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="166" s="3" customFormat="1" spans="1:9">
       <c r="A166" s="1">
         <v>3</v>
       </c>
@@ -14221,7 +14224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="167" s="3" customFormat="1" spans="1:9">
       <c r="A167" s="1">
         <v>4</v>
       </c>
@@ -14250,7 +14253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="168" s="3" customFormat="1" spans="1:9">
       <c r="A168" s="1">
         <v>5</v>
       </c>
@@ -14279,7 +14282,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" hidden="1" spans="1:9">
+    <row r="169" spans="1:9">
       <c r="A169" s="8">
         <v>6</v>
       </c>
@@ -14308,7 +14311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" hidden="1" spans="1:9">
+    <row r="170" spans="1:9">
       <c r="A170" s="8">
         <v>7</v>
       </c>
@@ -14337,7 +14340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" hidden="1" spans="1:9">
+    <row r="171" spans="1:9">
       <c r="A171" s="8">
         <v>8</v>
       </c>
@@ -14363,7 +14366,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" hidden="1" spans="1:9">
+    <row r="172" spans="1:9">
       <c r="A172" s="8">
         <v>9</v>
       </c>
@@ -14389,7 +14392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="1:9">
+    <row r="173" spans="1:9">
       <c r="A173" s="8">
         <v>9</v>
       </c>
@@ -14418,7 +14421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="1:9">
+    <row r="174" spans="1:9">
       <c r="A174" s="8">
         <v>11</v>
       </c>
@@ -14447,7 +14450,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" hidden="1" spans="1:9">
+    <row r="175" spans="1:9">
       <c r="A175" s="8">
         <v>12</v>
       </c>
@@ -14476,7 +14479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" hidden="1" spans="1:9">
+    <row r="176" spans="1:9">
       <c r="A176" s="8">
         <v>13</v>
       </c>
@@ -14505,7 +14508,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" hidden="1" spans="1:9">
+    <row r="177" spans="1:9">
       <c r="A177" s="8">
         <v>14</v>
       </c>
@@ -14531,7 +14534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" hidden="1" spans="1:9">
+    <row r="178" spans="1:9">
       <c r="A178" s="8">
         <v>14</v>
       </c>
@@ -14557,7 +14560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="1:9">
+    <row r="179" spans="1:9">
       <c r="A179" s="8">
         <v>16</v>
       </c>
@@ -14583,7 +14586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" hidden="1" spans="1:9">
+    <row r="180" spans="1:9">
       <c r="A180" s="8">
         <v>16</v>
       </c>
@@ -14609,7 +14612,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="181" s="3" customFormat="1" spans="1:9">
       <c r="A181" s="1">
         <v>1</v>
       </c>
@@ -14638,7 +14641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="182" s="3" customFormat="1" spans="1:9">
       <c r="A182" s="1">
         <v>2</v>
       </c>
@@ -14667,7 +14670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183" hidden="1" spans="1:9">
+    <row r="183" spans="1:9">
       <c r="A183" s="8">
         <v>3</v>
       </c>
@@ -14693,7 +14696,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" hidden="1" spans="1:9">
+    <row r="184" spans="1:9">
       <c r="A184" s="8">
         <v>4</v>
       </c>
@@ -14722,7 +14725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" hidden="1" spans="1:9">
+    <row r="185" spans="1:9">
       <c r="A185" s="8">
         <v>5</v>
       </c>
@@ -14748,7 +14751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" hidden="1" spans="1:9">
+    <row r="186" spans="1:9">
       <c r="A186" s="8">
         <v>6</v>
       </c>
@@ -14774,7 +14777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" hidden="1" spans="1:9">
+    <row r="187" spans="1:9">
       <c r="A187" s="8">
         <v>7</v>
       </c>
@@ -14800,7 +14803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" hidden="1" spans="1:9">
+    <row r="188" spans="1:9">
       <c r="A188" s="8">
         <v>8</v>
       </c>
@@ -14829,7 +14832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="189" hidden="1" spans="1:9">
+    <row r="189" spans="1:9">
       <c r="A189" s="8">
         <v>9</v>
       </c>
@@ -14855,7 +14858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" hidden="1" spans="1:9">
+    <row r="190" spans="1:9">
       <c r="A190" s="8">
         <v>10</v>
       </c>
@@ -14884,7 +14887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" hidden="1" spans="1:9">
+    <row r="191" spans="1:9">
       <c r="A191" s="8">
         <v>11</v>
       </c>
@@ -14913,7 +14916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" hidden="1" spans="1:9">
+    <row r="192" spans="1:9">
       <c r="A192" s="8">
         <v>12</v>
       </c>
@@ -14939,7 +14942,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" hidden="1" spans="1:9">
+    <row r="193" spans="1:9">
       <c r="A193" s="8">
         <v>13</v>
       </c>
@@ -14965,7 +14968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" hidden="1" spans="1:9">
+    <row r="194" spans="1:9">
       <c r="A194" s="8">
         <v>14</v>
       </c>
@@ -14991,7 +14994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" hidden="1" spans="1:9">
+    <row r="195" spans="1:9">
       <c r="A195" s="8">
         <v>15</v>
       </c>
@@ -15017,7 +15020,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" hidden="1" spans="1:9">
+    <row r="196" spans="1:9">
       <c r="A196" s="8">
         <v>16</v>
       </c>
@@ -15043,7 +15046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" hidden="1" spans="1:9">
+    <row r="197" spans="1:9">
       <c r="A197" s="8">
         <v>17</v>
       </c>
@@ -15069,7 +15072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="198" s="3" customFormat="1" spans="1:9">
       <c r="A198" s="1">
         <v>1</v>
       </c>
@@ -15098,7 +15101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="199" s="3" customFormat="1" spans="1:9">
       <c r="A199" s="1">
         <v>2</v>
       </c>
@@ -15127,7 +15130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" hidden="1" spans="1:9">
+    <row r="200" spans="1:9">
       <c r="A200" s="8">
         <v>3</v>
       </c>
@@ -15156,7 +15159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" hidden="1" spans="1:9">
+    <row r="201" spans="1:9">
       <c r="A201" s="8">
         <v>4</v>
       </c>
@@ -15182,7 +15185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" hidden="1" spans="1:9">
+    <row r="202" spans="1:9">
       <c r="A202" s="8">
         <v>5</v>
       </c>
@@ -15208,7 +15211,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" hidden="1" spans="1:9">
+    <row r="203" spans="1:9">
       <c r="A203" s="8">
         <v>6</v>
       </c>
@@ -15235,7 +15238,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" hidden="1" spans="1:9">
+    <row r="204" spans="1:9">
       <c r="A204" s="8">
         <v>7</v>
       </c>
@@ -15261,7 +15264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" hidden="1" spans="1:9">
+    <row r="205" spans="1:9">
       <c r="A205" s="8">
         <v>8</v>
       </c>
@@ -15288,7 +15291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" hidden="1" spans="1:9">
+    <row r="206" spans="1:9">
       <c r="A206" s="8">
         <v>9</v>
       </c>
@@ -15314,7 +15317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" hidden="1" spans="1:9">
+    <row r="207" spans="1:9">
       <c r="A207" s="8">
         <v>10</v>
       </c>
@@ -15340,7 +15343,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" hidden="1" spans="1:9">
+    <row r="208" spans="1:9">
       <c r="A208" s="8">
         <v>11</v>
       </c>
@@ -15366,7 +15369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" hidden="1" spans="1:9">
+    <row r="209" spans="1:9">
       <c r="A209" s="8" t="s">
         <v>83</v>
       </c>
@@ -15392,7 +15395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="210" s="3" customFormat="1" spans="1:9">
       <c r="A210" s="1">
         <v>1</v>
       </c>
@@ -15421,7 +15424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="211" s="3" customFormat="1" spans="1:9">
       <c r="A211" s="1">
         <v>2</v>
       </c>
@@ -15450,7 +15453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="212" s="3" customFormat="1" spans="1:9">
       <c r="A212" s="1">
         <v>3</v>
       </c>
@@ -15479,7 +15482,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" hidden="1" spans="1:9">
+    <row r="213" spans="1:9">
       <c r="A213" s="8">
         <v>4</v>
       </c>
@@ -15508,7 +15511,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" hidden="1" spans="1:9">
+    <row r="214" spans="1:9">
       <c r="A214" s="8">
         <v>5</v>
       </c>
@@ -15537,7 +15540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" hidden="1" spans="1:9">
+    <row r="215" spans="1:9">
       <c r="A215" s="8">
         <v>6</v>
       </c>
@@ -15563,7 +15566,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" hidden="1" spans="1:9">
+    <row r="216" spans="1:9">
       <c r="A216" s="8">
         <v>7</v>
       </c>
@@ -15592,7 +15595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" hidden="1" spans="1:9">
+    <row r="217" spans="1:9">
       <c r="A217" s="8">
         <v>8</v>
       </c>
@@ -15618,7 +15621,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" hidden="1" spans="1:9">
+    <row r="218" spans="1:9">
       <c r="A218" s="8">
         <v>9</v>
       </c>
@@ -15644,7 +15647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" hidden="1" spans="1:9">
+    <row r="219" spans="1:9">
       <c r="A219" s="8">
         <v>10</v>
       </c>
@@ -15673,7 +15676,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" hidden="1" spans="1:9">
+    <row r="220" spans="1:9">
       <c r="A220" s="8">
         <v>11</v>
       </c>
@@ -15699,7 +15702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" hidden="1" spans="1:9">
+    <row r="221" spans="1:9">
       <c r="A221" s="8">
         <v>12</v>
       </c>
@@ -15725,7 +15728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" hidden="1" spans="1:9">
+    <row r="222" spans="1:9">
       <c r="A222" s="8">
         <v>13</v>
       </c>
@@ -15754,7 +15757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" hidden="1" spans="1:9">
+    <row r="223" spans="1:9">
       <c r="A223" s="8">
         <v>14</v>
       </c>
@@ -15780,7 +15783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" hidden="1" spans="1:9">
+    <row r="224" spans="1:9">
       <c r="A224" s="8">
         <v>15</v>
       </c>
@@ -15806,7 +15809,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" hidden="1" spans="1:9">
+    <row r="225" spans="1:9">
       <c r="A225" s="8">
         <v>16</v>
       </c>
@@ -15832,7 +15835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" hidden="1" spans="1:9">
+    <row r="226" spans="1:9">
       <c r="A226" s="8">
         <v>17</v>
       </c>
@@ -15858,7 +15861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" hidden="1" spans="1:9">
+    <row r="227" spans="1:9">
       <c r="A227" s="8">
         <v>18</v>
       </c>
@@ -15884,7 +15887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" hidden="1" spans="1:9">
+    <row r="228" spans="1:9">
       <c r="A228" s="8">
         <v>19</v>
       </c>
@@ -15910,7 +15913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" hidden="1" spans="1:9">
+    <row r="229" spans="1:9">
       <c r="A229" s="8">
         <v>20</v>
       </c>
@@ -15936,7 +15939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" hidden="1" spans="1:9">
+    <row r="230" spans="1:9">
       <c r="A230" s="8">
         <v>1</v>
       </c>
@@ -15962,7 +15965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" hidden="1" spans="1:9">
+    <row r="231" spans="1:9">
       <c r="A231" s="8">
         <v>2</v>
       </c>
@@ -15991,7 +15994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" hidden="1" spans="1:9">
+    <row r="232" spans="1:9">
       <c r="A232" s="8">
         <v>3</v>
       </c>
@@ -16020,7 +16023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" hidden="1" spans="1:9">
+    <row r="233" spans="1:9">
       <c r="A233" s="8">
         <v>4</v>
       </c>
@@ -16046,7 +16049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" hidden="1" spans="1:9">
+    <row r="234" spans="1:9">
       <c r="A234" s="8">
         <v>5</v>
       </c>
@@ -16072,7 +16075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" hidden="1" spans="1:9">
+    <row r="235" spans="1:9">
       <c r="A235" s="8">
         <v>6</v>
       </c>
@@ -16098,7 +16101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" hidden="1" spans="1:9">
+    <row r="236" spans="1:9">
       <c r="A236" s="8">
         <v>7</v>
       </c>
@@ -16124,7 +16127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" hidden="1" spans="1:9">
+    <row r="237" spans="1:9">
       <c r="A237" s="8">
         <v>8</v>
       </c>
@@ -16153,7 +16156,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" hidden="1" spans="1:9">
+    <row r="238" spans="1:9">
       <c r="A238" s="8">
         <v>9</v>
       </c>
@@ -16180,7 +16183,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" hidden="1" spans="1:9">
+    <row r="239" spans="1:9">
       <c r="A239" s="8">
         <v>10</v>
       </c>
@@ -16206,7 +16209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" hidden="1" spans="1:9">
+    <row r="240" spans="1:9">
       <c r="A240" s="8">
         <v>11</v>
       </c>
@@ -16232,7 +16235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" hidden="1" spans="1:9">
+    <row r="241" spans="1:9">
       <c r="A241" s="8" t="s">
         <v>83</v>
       </c>
@@ -16258,7 +16261,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="242" s="3" customFormat="1" spans="1:9">
       <c r="A242" s="1">
         <v>1</v>
       </c>
@@ -16287,7 +16290,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="243" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="243" s="3" customFormat="1" spans="1:9">
       <c r="A243" s="1">
         <v>2</v>
       </c>
@@ -16316,7 +16319,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="244" hidden="1" spans="1:9">
+    <row r="244" spans="1:9">
       <c r="A244" s="8">
         <v>3</v>
       </c>
@@ -16345,7 +16348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" hidden="1" spans="1:9">
+    <row r="245" spans="1:9">
       <c r="A245" s="8">
         <v>4</v>
       </c>
@@ -16371,7 +16374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" hidden="1" spans="1:9">
+    <row r="246" spans="1:9">
       <c r="A246" s="8">
         <v>5</v>
       </c>
@@ -16400,7 +16403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" hidden="1" spans="1:9">
+    <row r="247" spans="1:9">
       <c r="A247" s="8">
         <v>6</v>
       </c>
@@ -16426,7 +16429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" hidden="1" spans="1:9">
+    <row r="248" spans="1:9">
       <c r="A248" s="8">
         <v>7</v>
       </c>
@@ -16452,7 +16455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" hidden="1" spans="1:9">
+    <row r="249" spans="1:9">
       <c r="A249" s="8">
         <v>8</v>
       </c>
@@ -16478,7 +16481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="250" s="3" customFormat="1" spans="1:9">
       <c r="A250" s="1">
         <v>1</v>
       </c>
@@ -16507,7 +16510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="251" s="3" customFormat="1" spans="1:9">
       <c r="A251" s="1">
         <v>2</v>
       </c>
@@ -16536,7 +16539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="252" s="3" customFormat="1" spans="1:9">
       <c r="A252" s="1">
         <v>3</v>
       </c>
@@ -16565,7 +16568,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" hidden="1" spans="1:9">
+    <row r="253" spans="1:9">
       <c r="A253" s="8">
         <v>4</v>
       </c>
@@ -16594,7 +16597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="254" hidden="1" spans="1:9">
+    <row r="254" spans="1:9">
       <c r="A254" s="8">
         <v>5</v>
       </c>
@@ -16620,7 +16623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" hidden="1" spans="1:9">
+    <row r="255" spans="1:9">
       <c r="A255" s="8">
         <v>6</v>
       </c>
@@ -16646,7 +16649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="256" hidden="1" spans="1:9">
+    <row r="256" spans="1:9">
       <c r="A256" s="8">
         <v>7</v>
       </c>
@@ -16672,7 +16675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="257" hidden="1" spans="1:9">
+    <row r="257" spans="1:9">
       <c r="A257" s="8">
         <v>8</v>
       </c>
@@ -16698,7 +16701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="258" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="258" s="3" customFormat="1" spans="1:9">
       <c r="A258" s="1">
         <v>1</v>
       </c>
@@ -16727,7 +16730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="259" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="259" s="3" customFormat="1" spans="1:9">
       <c r="A259" s="1">
         <v>2</v>
       </c>
@@ -16756,7 +16759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="260" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="260" s="3" customFormat="1" spans="1:9">
       <c r="A260" s="1">
         <v>3</v>
       </c>
@@ -16785,7 +16788,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="261" s="3" customFormat="1" spans="1:9">
       <c r="A261" s="1">
         <v>4</v>
       </c>
@@ -16814,7 +16817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="262" s="3" customFormat="1" spans="1:9">
       <c r="A262" s="1">
         <v>5</v>
       </c>
@@ -16843,7 +16846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="263" hidden="1" spans="1:9">
+    <row r="263" spans="1:9">
       <c r="A263" s="8">
         <v>6</v>
       </c>
@@ -16872,7 +16875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="264" hidden="1" spans="1:9">
+    <row r="264" spans="1:9">
       <c r="A264" s="8">
         <v>7</v>
       </c>
@@ -16901,7 +16904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="265" hidden="1" spans="1:9">
+    <row r="265" spans="1:9">
       <c r="A265" s="8">
         <v>8</v>
       </c>
@@ -16930,7 +16933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" hidden="1" spans="1:9">
+    <row r="266" spans="1:9">
       <c r="A266" s="8">
         <v>9</v>
       </c>
@@ -16959,7 +16962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" hidden="1" spans="1:9">
+    <row r="267" spans="1:9">
       <c r="A267" s="8">
         <v>10</v>
       </c>
@@ -16988,7 +16991,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="268" hidden="1" spans="1:9">
+    <row r="268" spans="1:9">
       <c r="A268" s="8">
         <v>11</v>
       </c>
@@ -17014,7 +17017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="269" hidden="1" spans="1:9">
+    <row r="269" spans="1:9">
       <c r="A269" s="8">
         <v>12</v>
       </c>
@@ -17040,7 +17043,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="270" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="270" s="3" customFormat="1" spans="1:9">
       <c r="A270" s="1">
         <v>1</v>
       </c>
@@ -17069,7 +17072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="271" s="3" customFormat="1" spans="1:9">
       <c r="A271" s="1">
         <v>2</v>
       </c>
@@ -17098,7 +17101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="272" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="272" s="3" customFormat="1" spans="1:9">
       <c r="A272" s="1">
         <v>3</v>
       </c>
@@ -17127,7 +17130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="273" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="273" s="3" customFormat="1" spans="1:9">
       <c r="A273" s="1">
         <v>4</v>
       </c>
@@ -17156,7 +17159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" hidden="1" spans="1:9">
+    <row r="274" spans="1:9">
       <c r="A274" s="8">
         <v>5</v>
       </c>
@@ -17185,7 +17188,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="275" hidden="1" spans="1:9">
+    <row r="275" spans="1:9">
       <c r="A275" s="8">
         <v>6</v>
       </c>
@@ -17211,7 +17214,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="276" hidden="1" spans="1:9">
+    <row r="276" spans="1:9">
       <c r="A276" s="8">
         <v>7</v>
       </c>
@@ -17237,7 +17240,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="277" hidden="1" spans="1:9">
+    <row r="277" spans="1:9">
       <c r="A277" s="8">
         <v>8</v>
       </c>
@@ -17266,7 +17269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="278" hidden="1" spans="1:9">
+    <row r="278" spans="1:9">
       <c r="A278" s="8">
         <v>9</v>
       </c>
@@ -17292,7 +17295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="279" hidden="1" spans="1:9">
+    <row r="279" spans="1:9">
       <c r="A279" s="8">
         <v>10</v>
       </c>
@@ -17318,7 +17321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="280" hidden="1" spans="1:9">
+    <row r="280" spans="1:9">
       <c r="A280" s="8">
         <v>11</v>
       </c>
@@ -17344,7 +17347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" hidden="1" spans="1:9">
+    <row r="281" spans="1:9">
       <c r="A281" s="8">
         <v>12</v>
       </c>
@@ -17370,7 +17373,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="282" s="3" customFormat="1" spans="1:9">
       <c r="A282" s="1">
         <v>1</v>
       </c>
@@ -17399,7 +17402,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" hidden="1" spans="1:9">
+    <row r="283" spans="1:9">
       <c r="A283" s="8">
         <v>2</v>
       </c>
@@ -17428,7 +17431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" hidden="1" spans="1:9">
+    <row r="284" spans="1:9">
       <c r="A284" s="8">
         <v>3</v>
       </c>
@@ -17454,7 +17457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="285" hidden="1" spans="1:9">
+    <row r="285" spans="1:9">
       <c r="A285" s="8">
         <v>4</v>
       </c>
@@ -17480,7 +17483,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="286" hidden="1" spans="1:9">
+    <row r="286" spans="1:9">
       <c r="A286" s="8">
         <v>5</v>
       </c>
@@ -17506,7 +17509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="287" hidden="1" spans="1:9">
+    <row r="287" spans="1:9">
       <c r="A287" s="8">
         <v>6</v>
       </c>
@@ -17532,7 +17535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="288" hidden="1" spans="1:9">
+    <row r="288" spans="1:9">
       <c r="A288" s="8">
         <v>7</v>
       </c>
@@ -17558,7 +17561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" hidden="1" spans="1:9">
+    <row r="289" spans="1:9">
       <c r="A289" s="8">
         <v>8</v>
       </c>
@@ -17584,7 +17587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" hidden="1" spans="1:9">
+    <row r="290" spans="1:9">
       <c r="A290" s="8">
         <v>1</v>
       </c>
@@ -17613,7 +17616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="291" hidden="1" spans="1:9">
+    <row r="291" spans="1:9">
       <c r="A291" s="8">
         <v>2</v>
       </c>
@@ -17642,7 +17645,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="292" hidden="1" spans="1:9">
+    <row r="292" spans="1:9">
       <c r="A292" s="8">
         <v>3</v>
       </c>
@@ -17671,7 +17674,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="293" hidden="1" spans="1:9">
+    <row r="293" spans="1:9">
       <c r="A293" s="8">
         <v>4</v>
       </c>
@@ -17700,7 +17703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" hidden="1" spans="1:9">
+    <row r="294" spans="1:9">
       <c r="A294" s="8">
         <v>5</v>
       </c>
@@ -17726,7 +17729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="295" hidden="1" spans="1:9">
+    <row r="295" spans="1:9">
       <c r="A295" s="8">
         <v>6</v>
       </c>
@@ -17755,7 +17758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" hidden="1" spans="1:9">
+    <row r="296" spans="1:9">
       <c r="A296" s="8">
         <v>7</v>
       </c>
@@ -17781,7 +17784,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" hidden="1" spans="1:9">
+    <row r="297" spans="1:9">
       <c r="A297" s="8">
         <v>8</v>
       </c>
@@ -17810,7 +17813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="298" s="3" customFormat="1" spans="1:9">
       <c r="A298" s="1">
         <v>0</v>
       </c>
@@ -17839,7 +17842,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="299" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="299" s="3" customFormat="1" spans="1:9">
       <c r="A299" s="1">
         <v>0</v>
       </c>
@@ -17868,7 +17871,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="300" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="300" s="3" customFormat="1" spans="1:9">
       <c r="A300" s="1">
         <v>0</v>
       </c>
@@ -17897,7 +17900,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="301" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="301" s="3" customFormat="1" spans="1:9">
       <c r="A301" s="1">
         <v>0</v>
       </c>
@@ -17926,7 +17929,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="302" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="302" s="3" customFormat="1" spans="1:9">
       <c r="A302" s="1">
         <v>0</v>
       </c>
@@ -17955,7 +17958,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="303" s="3" customFormat="1" hidden="1" spans="1:9">
+    <row r="303" s="3" customFormat="1" spans="1:9">
       <c r="A303" s="1">
         <v>0</v>
       </c>
@@ -17984,7 +17987,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="304" hidden="1" spans="1:9">
+    <row r="304" spans="1:9">
       <c r="A304" s="8">
         <v>1</v>
       </c>
@@ -18010,7 +18013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="305" hidden="1" spans="1:9">
+    <row r="305" spans="1:9">
       <c r="A305" s="8">
         <v>2</v>
       </c>
@@ -18036,7 +18039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="306" hidden="1" spans="1:9">
+    <row r="306" spans="1:9">
       <c r="A306" s="8">
         <v>3</v>
       </c>
@@ -18062,7 +18065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="307" hidden="1" spans="1:9">
+    <row r="307" spans="1:9">
       <c r="A307" s="8">
         <v>4</v>
       </c>
@@ -18088,7 +18091,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" hidden="1" spans="1:9">
+    <row r="308" spans="1:9">
       <c r="A308" s="8">
         <v>5</v>
       </c>
@@ -18114,7 +18117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" hidden="1" spans="1:9">
+    <row r="309" spans="1:9">
       <c r="A309" s="8">
         <v>6</v>
       </c>
@@ -18140,7 +18143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" hidden="1" spans="1:9">
+    <row r="310" spans="1:9">
       <c r="A310" s="8">
         <v>7</v>
       </c>
@@ -18166,7 +18169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" hidden="1" spans="1:9">
+    <row r="311" spans="1:9">
       <c r="A311" s="8">
         <v>8</v>
       </c>
@@ -18192,7 +18195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="312" hidden="1" spans="1:9">
+    <row r="312" spans="1:9">
       <c r="A312" s="8">
         <v>9</v>
       </c>
@@ -18218,7 +18221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="313" hidden="1" spans="1:9">
+    <row r="313" spans="1:9">
       <c r="A313" s="8">
         <v>10</v>
       </c>
@@ -18244,7 +18247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="314" hidden="1" spans="1:9">
+    <row r="314" spans="1:9">
       <c r="A314" s="8">
         <v>11</v>
       </c>
@@ -18270,7 +18273,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="315" hidden="1" spans="1:9">
+    <row r="315" spans="1:9">
       <c r="A315" s="8">
         <v>12</v>
       </c>
@@ -18296,7 +18299,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="316" hidden="1" spans="1:9">
+    <row r="316" spans="1:9">
       <c r="A316" s="8">
         <v>13</v>
       </c>
@@ -18322,7 +18325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="317" hidden="1" spans="1:9">
+    <row r="317" spans="1:9">
       <c r="A317" s="8">
         <v>14</v>
       </c>
@@ -18348,7 +18351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" hidden="1" spans="1:9">
+    <row r="318" spans="1:9">
       <c r="A318" s="8">
         <v>15</v>
       </c>
@@ -18374,7 +18377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="319" hidden="1" spans="1:9">
+    <row r="319" spans="1:9">
       <c r="A319" s="8">
         <v>16</v>
       </c>
@@ -18400,7 +18403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" hidden="1" spans="1:9">
+    <row r="320" spans="1:9">
       <c r="A320" s="8">
         <v>17</v>
       </c>
@@ -18426,7 +18429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="321" hidden="1" spans="1:9">
+    <row r="321" spans="1:9">
       <c r="A321" s="8">
         <v>18</v>
       </c>
@@ -18452,7 +18455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" hidden="1" spans="1:9">
+    <row r="322" spans="1:9">
       <c r="A322" s="8">
         <v>19</v>
       </c>
@@ -18478,7 +18481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="323" hidden="1" spans="1:9">
+    <row r="323" spans="1:9">
       <c r="A323" s="8" t="s">
         <v>83</v>
       </c>
@@ -18504,7 +18507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:9">
+    <row r="324" spans="1:9">
       <c r="A324" s="8" t="s">
         <v>83</v>
       </c>
@@ -18530,7 +18533,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:9">
+    <row r="325" spans="1:9">
       <c r="A325" s="8" t="s">
         <v>83</v>
       </c>
@@ -18556,7 +18559,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="326" hidden="1" spans="1:9">
+    <row r="326" spans="1:9">
       <c r="A326" s="8" t="s">
         <v>83</v>
       </c>
@@ -18582,7 +18585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="327" hidden="1" spans="1:9">
+    <row r="327" spans="1:9">
       <c r="A327" s="8" t="s">
         <v>83</v>
       </c>
@@ -18608,7 +18611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="328" hidden="1" spans="1:9">
+    <row r="328" spans="1:9">
       <c r="A328" s="8" t="s">
         <v>83</v>
       </c>
@@ -18634,7 +18637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" hidden="1" spans="1:9">
+    <row r="329" spans="1:9">
       <c r="A329" s="8" t="s">
         <v>83</v>
       </c>
@@ -18660,7 +18663,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="330" hidden="1" spans="1:9">
+    <row r="330" spans="1:9">
       <c r="A330" s="8" t="s">
         <v>83</v>
       </c>
@@ -18686,7 +18689,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:9">
+    <row r="331" spans="1:9">
       <c r="A331" s="8">
         <v>0</v>
       </c>
@@ -18715,7 +18718,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="332" hidden="1" spans="1:9">
+    <row r="332" spans="1:9">
       <c r="A332" s="8">
         <v>1</v>
       </c>
@@ -18741,7 +18744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" hidden="1" spans="1:9">
+    <row r="333" spans="1:9">
       <c r="A333" s="8">
         <v>2</v>
       </c>
@@ -18767,7 +18770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="334" hidden="1" spans="1:9">
+    <row r="334" spans="1:9">
       <c r="A334" s="8">
         <v>3</v>
       </c>
@@ -18793,7 +18796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="335" hidden="1" spans="1:9">
+    <row r="335" spans="1:9">
       <c r="A335" s="8">
         <v>4</v>
       </c>
@@ -18819,7 +18822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" hidden="1" spans="1:9">
+    <row r="336" spans="1:9">
       <c r="A336" s="8">
         <v>5</v>
       </c>
@@ -18845,7 +18848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" hidden="1" spans="1:9">
+    <row r="337" spans="1:9">
       <c r="A337" s="8">
         <v>6</v>
       </c>
@@ -18871,7 +18874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" hidden="1" spans="1:9">
+    <row r="338" spans="1:9">
       <c r="A338" s="8">
         <v>7</v>
       </c>
@@ -18897,7 +18900,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="339" hidden="1" spans="1:9">
+    <row r="339" spans="1:9">
       <c r="A339" s="8">
         <v>8</v>
       </c>
@@ -18923,7 +18926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="340" hidden="1" spans="1:9">
+    <row r="340" spans="1:9">
       <c r="A340" s="8">
         <v>9</v>
       </c>
@@ -18949,7 +18952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="341" hidden="1" spans="1:9">
+    <row r="341" spans="1:9">
       <c r="A341" s="8">
         <v>10</v>
       </c>
@@ -18975,7 +18978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="342" hidden="1" spans="1:9">
+    <row r="342" spans="1:9">
       <c r="A342" s="8">
         <v>11</v>
       </c>
@@ -19001,7 +19004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="343" hidden="1" spans="1:9">
+    <row r="343" spans="1:9">
       <c r="A343" s="8">
         <v>12</v>
       </c>
@@ -19027,7 +19030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="344" hidden="1" spans="1:9">
+    <row r="344" spans="1:9">
       <c r="A344" s="8">
         <v>13</v>
       </c>
@@ -19053,7 +19056,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="345" hidden="1" spans="1:9">
+    <row r="345" spans="1:9">
       <c r="A345" s="8" t="s">
         <v>83</v>
       </c>
@@ -19079,7 +19082,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="346" hidden="1" spans="1:9">
+    <row r="346" spans="1:9">
       <c r="A346" s="8">
         <v>1</v>
       </c>
@@ -19105,7 +19108,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="347" hidden="1" spans="1:9">
+    <row r="347" spans="1:9">
       <c r="A347" s="8">
         <v>2</v>
       </c>
@@ -19134,7 +19137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="348" hidden="1" spans="1:9">
+    <row r="348" spans="1:9">
       <c r="A348" s="8">
         <v>3</v>
       </c>
@@ -19163,7 +19166,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="349" hidden="1" spans="1:9">
+    <row r="349" spans="1:9">
       <c r="A349" s="8">
         <v>4</v>
       </c>
@@ -19192,7 +19195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="350" hidden="1" spans="1:9">
+    <row r="350" spans="1:9">
       <c r="A350" s="8">
         <v>5</v>
       </c>
@@ -19221,7 +19224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="351" hidden="1" spans="1:9">
+    <row r="351" spans="1:9">
       <c r="A351" s="8">
         <v>6</v>
       </c>
@@ -19250,7 +19253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:9">
+    <row r="352" spans="1:9">
       <c r="A352" s="8">
         <v>7</v>
       </c>
@@ -19276,7 +19279,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="353" hidden="1" spans="1:9">
+    <row r="353" spans="1:9">
       <c r="A353" s="8">
         <v>8</v>
       </c>
@@ -19305,7 +19308,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="354" hidden="1" spans="1:9">
+    <row r="354" spans="1:9">
       <c r="A354" s="8" t="s">
         <v>83</v>
       </c>
@@ -19331,7 +19334,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:9">
+    <row r="355" spans="1:9">
       <c r="A355" s="8">
         <v>1</v>
       </c>
@@ -19360,7 +19363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:9">
+    <row r="356" spans="1:9">
       <c r="A356" s="8">
         <v>2</v>
       </c>
@@ -19389,7 +19392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:9">
+    <row r="357" spans="1:9">
       <c r="A357" s="8">
         <v>3</v>
       </c>
@@ -19418,7 +19421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:9">
+    <row r="358" spans="1:9">
       <c r="A358" s="8">
         <v>4</v>
       </c>
@@ -19444,7 +19447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:9">
+    <row r="359" spans="1:9">
       <c r="A359" s="8">
         <v>5</v>
       </c>
@@ -19470,7 +19473,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:9">
+    <row r="360" spans="1:9">
       <c r="A360" s="8" t="s">
         <v>83</v>
       </c>
@@ -19496,7 +19499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:9">
+    <row r="361" spans="1:9">
       <c r="A361" s="8" t="s">
         <v>83</v>
       </c>
@@ -19522,7 +19525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:9">
+    <row r="362" spans="1:9">
       <c r="A362" s="8" t="s">
         <v>83</v>
       </c>
@@ -19548,7 +19551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:9">
+    <row r="363" spans="1:9">
       <c r="A363" s="8">
         <v>1</v>
       </c>
@@ -19577,7 +19580,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:9">
+    <row r="364" spans="1:9">
       <c r="A364" s="8">
         <v>2</v>
       </c>
@@ -19606,7 +19609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:9">
+    <row r="365" spans="1:9">
       <c r="A365" s="8">
         <v>3</v>
       </c>
@@ -19632,7 +19635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:9">
+    <row r="366" spans="1:9">
       <c r="A366" s="8">
         <v>4</v>
       </c>
@@ -19661,7 +19664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:9">
+    <row r="367" spans="1:9">
       <c r="A367" s="8">
         <v>5</v>
       </c>
@@ -19690,7 +19693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:9">
+    <row r="368" spans="1:9">
       <c r="A368" s="8">
         <v>6</v>
       </c>
@@ -19719,7 +19722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:9">
+    <row r="369" spans="1:9">
       <c r="A369" s="8">
         <v>7</v>
       </c>
@@ -19745,7 +19748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:9">
+    <row r="370" spans="1:9">
       <c r="A370" s="8">
         <v>8</v>
       </c>
@@ -19771,7 +19774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:9">
+    <row r="371" spans="1:9">
       <c r="A371" s="8">
         <v>1</v>
       </c>
@@ -19800,7 +19803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="372" hidden="1" spans="1:9">
+    <row r="372" spans="1:9">
       <c r="A372" s="8">
         <v>2</v>
       </c>
@@ -19829,7 +19832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="373" hidden="1" spans="1:9">
+    <row r="373" spans="1:9">
       <c r="A373" s="8">
         <v>3</v>
       </c>
@@ -19858,7 +19861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="374" hidden="1" spans="1:9">
+    <row r="374" spans="1:9">
       <c r="A374" s="8">
         <v>4</v>
       </c>
@@ -19887,7 +19890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="375" hidden="1" spans="1:9">
+    <row r="375" spans="1:9">
       <c r="A375" s="8">
         <v>5</v>
       </c>
@@ -19916,7 +19919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:9">
+    <row r="376" spans="1:9">
       <c r="A376" s="8">
         <v>6</v>
       </c>
@@ -19945,7 +19948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="377" hidden="1" spans="1:9">
+    <row r="377" spans="1:9">
       <c r="A377" s="8">
         <v>7</v>
       </c>
@@ -19971,7 +19974,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:9">
+    <row r="378" spans="1:9">
       <c r="A378" s="8">
         <v>8</v>
       </c>
@@ -20000,7 +20003,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="379" hidden="1" spans="1:9">
+    <row r="379" spans="1:9">
       <c r="A379" s="8">
         <v>1</v>
       </c>
@@ -20026,7 +20029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:9">
+    <row r="380" spans="1:9">
       <c r="A380" s="8">
         <v>2</v>
       </c>
@@ -20055,7 +20058,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="381" hidden="1" spans="1:9">
+    <row r="381" spans="1:9">
       <c r="A381" s="8">
         <v>3</v>
       </c>
@@ -20081,7 +20084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:9">
+    <row r="382" spans="1:9">
       <c r="A382" s="8">
         <v>4</v>
       </c>
@@ -20110,7 +20113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:9">
+    <row r="383" spans="1:9">
       <c r="A383" s="8">
         <v>5</v>
       </c>
@@ -20136,7 +20139,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:9">
+    <row r="384" spans="1:9">
       <c r="A384" s="8">
         <v>6</v>
       </c>
@@ -20162,7 +20165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:9">
+    <row r="385" spans="1:9">
       <c r="A385" s="8">
         <v>7</v>
       </c>
@@ -20188,7 +20191,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:9">
+    <row r="386" spans="1:9">
       <c r="A386" s="8">
         <v>8</v>
       </c>
@@ -20214,7 +20217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:9">
+    <row r="387" spans="1:9">
       <c r="A387" s="8">
         <v>1</v>
       </c>
@@ -20243,7 +20246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:9">
+    <row r="388" spans="1:9">
       <c r="A388" s="8">
         <v>2</v>
       </c>
@@ -20272,7 +20275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:9">
+    <row r="389" spans="1:9">
       <c r="A389" s="8">
         <v>3</v>
       </c>
@@ -20301,7 +20304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:9">
+    <row r="390" spans="1:9">
       <c r="A390" s="8">
         <v>4</v>
       </c>
@@ -20330,7 +20333,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:9">
+    <row r="391" spans="1:9">
       <c r="A391" s="8">
         <v>5</v>
       </c>
@@ -20359,7 +20362,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:9">
+    <row r="392" spans="1:9">
       <c r="A392" s="8">
         <v>6</v>
       </c>
@@ -20388,7 +20391,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:9">
+    <row r="393" spans="1:9">
       <c r="A393" s="8">
         <v>7</v>
       </c>
@@ -20417,7 +20420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:9">
+    <row r="394" spans="1:9">
       <c r="A394" s="8">
         <v>8</v>
       </c>
@@ -20446,7 +20449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:9">
+    <row r="395" spans="1:9">
       <c r="A395" s="8">
         <v>9</v>
       </c>
@@ -20475,7 +20478,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="396" hidden="1" spans="1:9">
+    <row r="396" spans="1:9">
       <c r="A396" s="8">
         <v>10</v>
       </c>
@@ -20501,7 +20504,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:9">
+    <row r="397" spans="1:9">
       <c r="A397" s="8">
         <v>11</v>
       </c>
@@ -20530,7 +20533,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:9">
+    <row r="398" spans="1:9">
       <c r="A398" s="8">
         <v>12</v>
       </c>
@@ -20556,7 +20559,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="399" hidden="1" spans="1:9">
+    <row r="399" spans="1:9">
       <c r="A399" s="8">
         <v>13</v>
       </c>
@@ -20585,7 +20588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:9">
+    <row r="400" spans="1:9">
       <c r="A400" s="8">
         <v>14</v>
       </c>
@@ -20614,7 +20617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="401" hidden="1" spans="1:9">
+    <row r="401" spans="1:9">
       <c r="A401" s="8">
         <v>15</v>
       </c>
@@ -20640,7 +20643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="402" hidden="1" spans="1:9">
+    <row r="402" spans="1:9">
       <c r="A402" s="8">
         <v>16</v>
       </c>
@@ -20669,7 +20672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="403" hidden="1" spans="1:9">
+    <row r="403" spans="1:9">
       <c r="A403" s="8">
         <v>17</v>
       </c>
@@ -20698,7 +20701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" hidden="1" spans="1:9">
+    <row r="404" spans="1:9">
       <c r="A404" s="8">
         <v>18</v>
       </c>
@@ -20724,7 +20727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" hidden="1" spans="1:9">
+    <row r="405" spans="1:9">
       <c r="A405" s="8">
         <v>19</v>
       </c>
@@ -20750,7 +20753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="406" hidden="1" spans="1:9">
+    <row r="406" spans="1:9">
       <c r="A406" s="8">
         <v>20</v>
       </c>
@@ -20779,7 +20782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="407" hidden="1" spans="1:9">
+    <row r="407" spans="1:9">
       <c r="A407" s="8">
         <v>21</v>
       </c>
@@ -20805,7 +20808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="408" hidden="1" spans="1:9">
+    <row r="408" spans="1:9">
       <c r="A408" s="8">
         <v>22</v>
       </c>
@@ -20834,7 +20837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:9">
+    <row r="409" spans="1:9">
       <c r="A409" s="8">
         <v>23</v>
       </c>
@@ -20860,7 +20863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="410" hidden="1" spans="1:9">
+    <row r="410" spans="1:9">
       <c r="A410" s="8">
         <v>24</v>
       </c>
@@ -20889,7 +20892,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="411" hidden="1" spans="1:9">
+    <row r="411" spans="1:9">
       <c r="A411" s="8">
         <v>25</v>
       </c>
@@ -20918,7 +20921,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="412" hidden="1" spans="1:9">
+    <row r="412" spans="1:9">
       <c r="A412" s="8">
         <v>26</v>
       </c>
@@ -20944,7 +20947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="413" hidden="1" spans="1:9">
+    <row r="413" spans="1:9">
       <c r="A413" s="8">
         <v>27</v>
       </c>
@@ -20970,7 +20973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="414" hidden="1" spans="1:9">
+    <row r="414" spans="1:9">
       <c r="A414" s="8">
         <v>28</v>
       </c>
@@ -20999,7 +21002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="415" hidden="1" spans="1:9">
+    <row r="415" spans="1:9">
       <c r="A415" s="8" t="s">
         <v>83</v>
       </c>
@@ -21025,7 +21028,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="416" hidden="1" spans="1:9">
+    <row r="416" spans="1:9">
       <c r="A416" s="8">
         <v>1</v>
       </c>
@@ -21051,7 +21054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:9">
+    <row r="417" spans="1:9">
       <c r="A417" s="8">
         <v>2</v>
       </c>
@@ -21077,7 +21080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="418" hidden="1" spans="1:9">
+    <row r="418" spans="1:9">
       <c r="A418" s="8">
         <v>3</v>
       </c>
@@ -21106,7 +21109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="419" hidden="1" spans="1:9">
+    <row r="419" spans="1:9">
       <c r="A419" s="8">
         <v>4</v>
       </c>
@@ -21132,7 +21135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="420" hidden="1" spans="1:9">
+    <row r="420" spans="1:9">
       <c r="A420" s="8">
         <v>5</v>
       </c>
@@ -21161,7 +21164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="421" hidden="1" spans="1:9">
+    <row r="421" spans="1:9">
       <c r="A421" s="8">
         <v>6</v>
       </c>
@@ -21187,7 +21190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:9">
+    <row r="422" spans="1:9">
       <c r="A422" s="8">
         <v>7</v>
       </c>
@@ -21216,7 +21219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:9">
+    <row r="423" spans="1:9">
       <c r="A423" s="8">
         <v>8</v>
       </c>
@@ -21242,7 +21245,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="424" hidden="1" spans="1:9">
+    <row r="424" spans="1:9">
       <c r="A424" s="8">
         <v>9</v>
       </c>
@@ -21268,7 +21271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="425" hidden="1" spans="1:9">
+    <row r="425" spans="1:9">
       <c r="A425" s="8">
         <v>10</v>
       </c>
@@ -21297,7 +21300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:9">
+    <row r="426" spans="1:9">
       <c r="A426" s="8">
         <v>11</v>
       </c>
@@ -21326,7 +21329,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:9">
+    <row r="427" spans="1:9">
       <c r="A427" s="8">
         <v>12</v>
       </c>
@@ -21355,7 +21358,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:9">
+    <row r="428" spans="1:9">
       <c r="A428" s="8">
         <v>13</v>
       </c>
@@ -21384,7 +21387,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="429" hidden="1" spans="1:9">
+    <row r="429" spans="1:9">
       <c r="A429" s="8">
         <v>14</v>
       </c>
@@ -21410,7 +21413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:9">
+    <row r="430" spans="1:9">
       <c r="A430" s="8">
         <v>15</v>
       </c>
@@ -21436,7 +21439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:9">
+    <row r="431" spans="1:9">
       <c r="A431" s="8">
         <v>16</v>
       </c>
@@ -21462,7 +21465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:9">
+    <row r="432" spans="1:9">
       <c r="A432" s="8">
         <v>17</v>
       </c>
@@ -21491,7 +21494,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:9">
+    <row r="433" spans="1:9">
       <c r="A433" s="8">
         <v>1</v>
       </c>
@@ -21520,7 +21523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:9">
+    <row r="434" spans="1:9">
       <c r="A434" s="8">
         <v>2</v>
       </c>
@@ -21546,7 +21549,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:9">
+    <row r="435" spans="1:9">
       <c r="A435" s="8">
         <v>3</v>
       </c>
@@ -21575,7 +21578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="436" hidden="1" spans="1:9">
+    <row r="436" spans="1:9">
       <c r="A436" s="8">
         <v>4</v>
       </c>
@@ -21601,7 +21604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:9">
+    <row r="437" spans="1:9">
       <c r="A437" s="8">
         <v>5</v>
       </c>
@@ -21627,7 +21630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:9">
+    <row r="438" spans="1:9">
       <c r="A438" s="8">
         <v>6</v>
       </c>
@@ -21656,7 +21659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:9">
+    <row r="439" spans="1:9">
       <c r="A439" s="8">
         <v>7</v>
       </c>
@@ -21682,7 +21685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="440" hidden="1" spans="1:9">
+    <row r="440" spans="1:9">
       <c r="A440" s="8">
         <v>8</v>
       </c>
@@ -21708,7 +21711,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="441" hidden="1" spans="1:9">
+    <row r="441" spans="1:9">
       <c r="A441" s="8">
         <v>1</v>
       </c>
@@ -21737,7 +21740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="442" hidden="1" spans="1:9">
+    <row r="442" spans="1:9">
       <c r="A442" s="8">
         <v>2</v>
       </c>
@@ -21766,7 +21769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="443" hidden="1" spans="1:9">
+    <row r="443" spans="1:9">
       <c r="A443" s="8">
         <v>3</v>
       </c>
@@ -21795,7 +21798,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="444" hidden="1" spans="1:9">
+    <row r="444" spans="1:9">
       <c r="A444" s="8">
         <v>4</v>
       </c>
@@ -21824,7 +21827,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="445" hidden="1" spans="1:9">
+    <row r="445" spans="1:9">
       <c r="A445" s="8">
         <v>5</v>
       </c>
@@ -21853,7 +21856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:9">
+    <row r="446" spans="1:9">
       <c r="A446" s="8">
         <v>6</v>
       </c>
@@ -21879,7 +21882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="447" hidden="1" spans="1:9">
+    <row r="447" spans="1:9">
       <c r="A447" s="8">
         <v>7</v>
       </c>
@@ -21905,7 +21908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:9">
+    <row r="448" spans="1:9">
       <c r="A448" s="8">
         <v>8</v>
       </c>
@@ -21934,7 +21937,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="449" hidden="1" spans="1:9">
+    <row r="449" spans="1:9">
       <c r="A449" s="8">
         <v>1</v>
       </c>
@@ -21960,7 +21963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="450" hidden="1" spans="1:9">
+    <row r="450" spans="1:9">
       <c r="A450" s="8">
         <v>2</v>
       </c>
@@ -21989,7 +21992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="451" hidden="1" spans="1:9">
+    <row r="451" spans="1:9">
       <c r="A451" s="8">
         <v>3</v>
       </c>
@@ -22015,7 +22018,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="452" hidden="1" spans="1:9">
+    <row r="452" spans="1:9">
       <c r="A452" s="8">
         <v>4</v>
       </c>
@@ -22041,7 +22044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="453" hidden="1" spans="1:9">
+    <row r="453" spans="1:9">
       <c r="A453" s="8">
         <v>5</v>
       </c>
@@ -22067,7 +22070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="454" hidden="1" spans="1:9">
+    <row r="454" spans="1:9">
       <c r="A454" s="8">
         <v>6</v>
       </c>
@@ -22093,7 +22096,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="455" hidden="1" spans="1:9">
+    <row r="455" spans="1:9">
       <c r="A455" s="8">
         <v>7</v>
       </c>
@@ -22119,7 +22122,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="456" hidden="1" spans="1:9">
+    <row r="456" spans="1:9">
       <c r="A456" s="8">
         <v>8</v>
       </c>
@@ -22145,7 +22148,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="457" hidden="1" spans="1:9">
+    <row r="457" spans="1:9">
       <c r="A457" s="8">
         <v>9</v>
       </c>
@@ -22171,7 +22174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="458" hidden="1" spans="1:9">
+    <row r="458" spans="1:9">
       <c r="A458" s="8">
         <v>10</v>
       </c>
@@ -22200,7 +22203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="459" hidden="1" spans="1:9">
+    <row r="459" spans="1:9">
       <c r="A459" s="8">
         <v>11</v>
       </c>
@@ -22226,7 +22229,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="460" hidden="1" spans="1:9">
+    <row r="460" spans="1:9">
       <c r="A460" s="8">
         <v>12</v>
       </c>
@@ -22252,7 +22255,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="461" hidden="1" spans="1:9">
+    <row r="461" spans="1:9">
       <c r="A461" s="8">
         <v>13</v>
       </c>
@@ -22278,7 +22281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="462" hidden="1" spans="1:9">
+    <row r="462" spans="1:9">
       <c r="A462" s="8">
         <v>14</v>
       </c>
@@ -22304,7 +22307,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="463" hidden="1" spans="1:9">
+    <row r="463" spans="1:9">
       <c r="A463" s="8">
         <v>15</v>
       </c>
@@ -22330,7 +22333,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="464" hidden="1" spans="1:9">
+    <row r="464" spans="1:9">
       <c r="A464" s="8">
         <v>16</v>
       </c>
@@ -22356,7 +22359,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="465" hidden="1" spans="1:9">
+    <row r="465" spans="1:9">
       <c r="A465" s="8">
         <v>17</v>
       </c>
@@ -22382,7 +22385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="466" hidden="1" spans="1:9">
+    <row r="466" spans="1:9">
       <c r="A466" s="8">
         <v>18</v>
       </c>
@@ -22411,7 +22414,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="467" hidden="1" spans="1:9">
+    <row r="467" spans="1:9">
       <c r="A467" s="8">
         <v>19</v>
       </c>
@@ -22437,7 +22440,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="468" hidden="1" spans="1:9">
+    <row r="468" spans="1:9">
       <c r="A468" s="8">
         <v>20</v>
       </c>
@@ -22463,7 +22466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="469" hidden="1" spans="1:9">
+    <row r="469" spans="1:9">
       <c r="A469" s="8">
         <v>21</v>
       </c>
@@ -22489,7 +22492,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="470" hidden="1" spans="1:9">
+    <row r="470" spans="1:9">
       <c r="A470" s="8">
         <v>22</v>
       </c>
@@ -22515,7 +22518,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="471" hidden="1" spans="1:9">
+    <row r="471" spans="1:9">
       <c r="A471" s="8">
         <v>23</v>
       </c>
@@ -22541,7 +22544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="472" hidden="1" spans="1:9">
+    <row r="472" spans="1:9">
       <c r="A472" s="8">
         <v>24</v>
       </c>
@@ -22567,7 +22570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="473" hidden="1" spans="1:9">
+    <row r="473" spans="1:9">
       <c r="A473" s="8">
         <v>25</v>
       </c>
@@ -22593,7 +22596,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="474" hidden="1" spans="1:9">
+    <row r="474" spans="1:9">
       <c r="A474" s="8">
         <v>26</v>
       </c>
@@ -22622,7 +22625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="475" hidden="1" spans="1:9">
+    <row r="475" spans="1:9">
       <c r="A475" s="8">
         <v>27</v>
       </c>
@@ -22651,7 +22654,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="476" hidden="1" spans="1:9">
+    <row r="476" spans="1:9">
       <c r="A476" s="8">
         <v>28</v>
       </c>
@@ -22677,7 +22680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="477" hidden="1" spans="1:9">
+    <row r="477" spans="1:9">
       <c r="A477" s="8">
         <v>29</v>
       </c>
@@ -22703,7 +22706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="478" hidden="1" spans="1:9">
+    <row r="478" spans="1:9">
       <c r="A478" s="8">
         <v>30</v>
       </c>
@@ -22729,7 +22732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="479" hidden="1" spans="1:9">
+    <row r="479" spans="1:9">
       <c r="A479" s="8">
         <v>31</v>
       </c>
@@ -22755,7 +22758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="480" hidden="1" spans="1:9">
+    <row r="480" spans="1:9">
       <c r="A480" s="8">
         <v>32</v>
       </c>
@@ -22781,7 +22784,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="481" hidden="1" spans="1:9">
+    <row r="481" spans="1:9">
       <c r="A481" s="8">
         <v>33</v>
       </c>
@@ -22807,7 +22810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="482" hidden="1" spans="1:9">
+    <row r="482" spans="1:9">
       <c r="A482" s="8">
         <v>34</v>
       </c>
@@ -22833,7 +22836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="483" hidden="1" spans="1:9">
+    <row r="483" spans="1:9">
       <c r="A483" s="8">
         <v>35</v>
       </c>
@@ -22862,7 +22865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="484" hidden="1" spans="1:9">
+    <row r="484" spans="1:9">
       <c r="A484" s="8">
         <v>36</v>
       </c>
@@ -22888,7 +22891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="485" hidden="1" spans="1:9">
+    <row r="485" spans="1:9">
       <c r="A485" s="8">
         <v>37</v>
       </c>
@@ -22914,7 +22917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="486" hidden="1" spans="1:9">
+    <row r="486" spans="1:9">
       <c r="A486" s="8">
         <v>38</v>
       </c>
@@ -22943,7 +22946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="487" hidden="1" spans="1:9">
+    <row r="487" spans="1:9">
       <c r="A487" s="8">
         <v>39</v>
       </c>
@@ -22969,7 +22972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="488" hidden="1" spans="1:9">
+    <row r="488" spans="1:9">
       <c r="A488" s="8">
         <v>40</v>
       </c>
@@ -22995,7 +22998,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="489" hidden="1" spans="1:9">
+    <row r="489" spans="1:9">
       <c r="A489" s="8" t="s">
         <v>83</v>
       </c>
@@ -23021,7 +23024,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="490" hidden="1" spans="1:9">
+    <row r="490" spans="1:9">
       <c r="A490" s="8" t="s">
         <v>83</v>
       </c>
@@ -23047,7 +23050,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="491" hidden="1" spans="1:9">
+    <row r="491" spans="1:9">
       <c r="A491" s="8" t="s">
         <v>83</v>
       </c>
@@ -23073,7 +23076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="492" hidden="1" spans="1:9">
+    <row r="492" spans="1:9">
       <c r="A492" s="8" t="s">
         <v>83</v>
       </c>
@@ -23099,7 +23102,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="493" hidden="1" spans="1:9">
+    <row r="493" spans="1:9">
       <c r="A493" s="8" t="s">
         <v>83</v>
       </c>
@@ -23125,7 +23128,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="494" hidden="1" spans="1:9">
+    <row r="494" spans="1:9">
       <c r="A494" s="8" t="s">
         <v>83</v>
       </c>
@@ -23151,7 +23154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="495" hidden="1" spans="1:9">
+    <row r="495" spans="1:9">
       <c r="A495" s="8">
         <v>1</v>
       </c>
@@ -23177,7 +23180,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="496" hidden="1" spans="1:9">
+    <row r="496" spans="1:9">
       <c r="A496" s="8">
         <v>2</v>
       </c>
@@ -23203,7 +23206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="497" hidden="1" spans="1:9">
+    <row r="497" spans="1:9">
       <c r="A497" s="8">
         <v>3</v>
       </c>
@@ -23229,7 +23232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="498" hidden="1" spans="1:9">
+    <row r="498" spans="1:9">
       <c r="A498" s="8">
         <v>4</v>
       </c>
@@ -23255,7 +23258,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="499" hidden="1" spans="1:9">
+    <row r="499" spans="1:9">
       <c r="A499" s="8">
         <v>5</v>
       </c>
@@ -23281,7 +23284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="500" hidden="1" spans="1:9">
+    <row r="500" spans="1:9">
       <c r="A500" s="8">
         <v>6</v>
       </c>
@@ -23307,7 +23310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="501" hidden="1" spans="1:9">
+    <row r="501" spans="1:9">
       <c r="A501" s="8">
         <v>7</v>
       </c>
@@ -23333,7 +23336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="502" hidden="1" spans="1:9">
+    <row r="502" spans="1:9">
       <c r="A502" s="8">
         <v>8</v>
       </c>
@@ -23359,7 +23362,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="503" hidden="1" spans="1:9">
+    <row r="503" spans="1:9">
       <c r="A503" s="8">
         <v>9</v>
       </c>
@@ -23385,7 +23388,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="504" hidden="1" spans="1:9">
+    <row r="504" spans="1:9">
       <c r="A504" s="8">
         <v>10</v>
       </c>
@@ -23411,7 +23414,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="505" hidden="1" spans="1:9">
+    <row r="505" spans="1:9">
       <c r="A505" s="8">
         <v>11</v>
       </c>
@@ -23437,7 +23440,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="506" hidden="1" spans="1:9">
+    <row r="506" spans="1:9">
       <c r="A506" s="8">
         <v>12</v>
       </c>
@@ -23463,7 +23466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="507" hidden="1" spans="1:9">
+    <row r="507" spans="1:9">
       <c r="A507" s="8">
         <v>13</v>
       </c>
@@ -23489,7 +23492,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="508" hidden="1" spans="1:9">
+    <row r="508" spans="1:9">
       <c r="A508" s="8">
         <v>14</v>
       </c>
@@ -23515,7 +23518,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="509" hidden="1" spans="1:9">
+    <row r="509" spans="1:9">
       <c r="A509" s="8">
         <v>15</v>
       </c>
@@ -23541,7 +23544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="510" hidden="1" spans="1:9">
+    <row r="510" spans="1:9">
       <c r="A510" s="8">
         <v>16</v>
       </c>
@@ -23567,7 +23570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="511" hidden="1" spans="1:9">
+    <row r="511" spans="1:9">
       <c r="A511" s="8">
         <v>17</v>
       </c>
@@ -23593,7 +23596,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="512" hidden="1" spans="1:9">
+    <row r="512" spans="1:9">
       <c r="A512" s="8">
         <v>18</v>
       </c>
@@ -23619,7 +23622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="513" hidden="1" spans="1:9">
+    <row r="513" spans="1:9">
       <c r="A513" s="8">
         <v>19</v>
       </c>
@@ -23645,7 +23648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="514" hidden="1" spans="1:9">
+    <row r="514" spans="1:9">
       <c r="A514" s="8">
         <v>20</v>
       </c>
@@ -23671,7 +23674,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="515" hidden="1" spans="1:9">
+    <row r="515" spans="1:9">
       <c r="A515" s="8">
         <v>21</v>
       </c>
@@ -23697,7 +23700,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="516" hidden="1" spans="1:9">
+    <row r="516" spans="1:9">
       <c r="A516" s="8">
         <v>22</v>
       </c>
@@ -23726,7 +23729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="517" hidden="1" spans="1:9">
+    <row r="517" spans="1:9">
       <c r="A517" s="8">
         <v>23</v>
       </c>
@@ -23752,7 +23755,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="518" hidden="1" spans="1:9">
+    <row r="518" spans="1:9">
       <c r="A518" s="8">
         <v>24</v>
       </c>
@@ -23778,7 +23781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="519" hidden="1" spans="1:9">
+    <row r="519" spans="1:9">
       <c r="A519" s="8">
         <v>25</v>
       </c>
@@ -23804,7 +23807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="520" hidden="1" spans="1:9">
+    <row r="520" spans="1:9">
       <c r="A520" s="8">
         <v>26</v>
       </c>
@@ -23830,7 +23833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="521" hidden="1" spans="1:9">
+    <row r="521" spans="1:9">
       <c r="A521" s="8">
         <v>27</v>
       </c>
@@ -23859,7 +23862,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="522" hidden="1" spans="1:9">
+    <row r="522" spans="1:9">
       <c r="A522" s="8">
         <v>28</v>
       </c>
@@ -23885,7 +23888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="523" hidden="1" spans="1:9">
+    <row r="523" spans="1:9">
       <c r="A523" s="8">
         <v>29</v>
       </c>
@@ -23911,7 +23914,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="524" hidden="1" spans="1:9">
+    <row r="524" spans="1:9">
       <c r="A524" s="8">
         <v>30</v>
       </c>
@@ -23937,7 +23940,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="525" hidden="1" spans="1:9">
+    <row r="525" spans="1:9">
       <c r="A525" s="8">
         <v>31</v>
       </c>
@@ -23966,7 +23969,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="526" hidden="1" spans="1:9">
+    <row r="526" spans="1:9">
       <c r="A526" s="8">
         <v>32</v>
       </c>
@@ -23992,7 +23995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="527" hidden="1" spans="1:9">
+    <row r="527" spans="1:9">
       <c r="A527" s="8">
         <v>33</v>
       </c>
@@ -24018,7 +24021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="528" hidden="1" spans="1:9">
+    <row r="528" spans="1:9">
       <c r="A528" s="8">
         <v>34</v>
       </c>
@@ -24044,7 +24047,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="529" hidden="1" spans="1:9">
+    <row r="529" spans="1:9">
       <c r="A529" s="8">
         <v>35</v>
       </c>
@@ -24070,7 +24073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="530" hidden="1" spans="1:9">
+    <row r="530" spans="1:9">
       <c r="A530" s="8">
         <v>36</v>
       </c>
@@ -24099,7 +24102,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="531" hidden="1" spans="1:9">
+    <row r="531" spans="1:9">
       <c r="A531" s="8">
         <v>37</v>
       </c>
@@ -24125,7 +24128,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="532" hidden="1" spans="1:9">
+    <row r="532" spans="1:9">
       <c r="A532" s="8">
         <v>38</v>
       </c>
@@ -24151,7 +24154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="533" hidden="1" spans="1:9">
+    <row r="533" spans="1:9">
       <c r="A533" s="8">
         <v>39</v>
       </c>
@@ -24177,7 +24180,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="534" hidden="1" spans="1:9">
+    <row r="534" spans="1:9">
       <c r="A534" s="8">
         <v>40</v>
       </c>
@@ -24203,7 +24206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="535" hidden="1" spans="1:9">
+    <row r="535" spans="1:9">
       <c r="A535" s="8">
         <v>41</v>
       </c>
@@ -24229,7 +24232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="536" hidden="1" spans="1:9">
+    <row r="536" spans="1:9">
       <c r="A536" s="8">
         <v>42</v>
       </c>
@@ -24255,7 +24258,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="537" hidden="1" spans="1:9">
+    <row r="537" spans="1:9">
       <c r="A537" s="8">
         <v>43</v>
       </c>
@@ -24281,7 +24284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="538" hidden="1" spans="1:9">
+    <row r="538" spans="1:9">
       <c r="A538" s="8">
         <v>44</v>
       </c>
@@ -24310,7 +24313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="539" hidden="1" spans="1:9">
+    <row r="539" spans="1:9">
       <c r="A539" s="8">
         <v>45</v>
       </c>
@@ -24336,7 +24339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="540" hidden="1" spans="1:9">
+    <row r="540" spans="1:9">
       <c r="A540" s="8">
         <v>46</v>
       </c>
@@ -24362,7 +24365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="541" hidden="1" spans="1:9">
+    <row r="541" spans="1:9">
       <c r="A541" s="8">
         <v>47</v>
       </c>
@@ -24388,7 +24391,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="542" hidden="1" spans="1:9">
+    <row r="542" spans="1:9">
       <c r="A542" s="8" t="s">
         <v>83</v>
       </c>
@@ -24414,7 +24417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="543" hidden="1" spans="1:9">
+    <row r="543" spans="1:9">
       <c r="A543" s="8" t="s">
         <v>83</v>
       </c>
@@ -24440,7 +24443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="544" hidden="1" spans="1:9">
+    <row r="544" spans="1:9">
       <c r="A544" s="8" t="s">
         <v>83</v>
       </c>
@@ -24466,7 +24469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="545" hidden="1" spans="1:9">
+    <row r="545" spans="1:9">
       <c r="A545" s="8" t="s">
         <v>83</v>
       </c>
@@ -24492,7 +24495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="546" hidden="1" spans="1:9">
+    <row r="546" spans="1:9">
       <c r="A546" s="8" t="s">
         <v>83</v>
       </c>
@@ -24518,7 +24521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="547" hidden="1" spans="1:9">
+    <row r="547" spans="1:9">
       <c r="A547" s="8" t="s">
         <v>83</v>
       </c>
@@ -24544,7 +24547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="548" hidden="1" spans="1:9">
+    <row r="548" spans="1:9">
       <c r="A548" s="8" t="s">
         <v>83</v>
       </c>
@@ -24570,7 +24573,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="549" hidden="1" spans="1:9">
+    <row r="549" spans="1:9">
       <c r="A549" s="8" t="s">
         <v>83</v>
       </c>
@@ -24596,7 +24599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="550" hidden="1" spans="1:9">
+    <row r="550" spans="1:9">
       <c r="A550" s="8" t="s">
         <v>83</v>
       </c>
@@ -24622,7 +24625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="551" hidden="1" spans="1:9">
+    <row r="551" spans="1:9">
       <c r="A551" s="8" t="s">
         <v>83</v>
       </c>
@@ -24648,7 +24651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="552" hidden="1" spans="1:9">
+    <row r="552" spans="1:9">
       <c r="A552" s="8" t="s">
         <v>83</v>
       </c>
@@ -24674,7 +24677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="553" hidden="1" spans="1:9">
+    <row r="553" spans="1:9">
       <c r="A553" s="8">
         <v>1</v>
       </c>
@@ -24703,7 +24706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="554" hidden="1" spans="1:9">
+    <row r="554" spans="1:9">
       <c r="A554" s="8">
         <v>2</v>
       </c>
@@ -24729,7 +24732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="555" hidden="1" spans="1:9">
+    <row r="555" spans="1:9">
       <c r="A555" s="8">
         <v>3</v>
       </c>
@@ -24755,7 +24758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="556" hidden="1" spans="1:9">
+    <row r="556" spans="1:9">
       <c r="A556" s="8">
         <v>4</v>
       </c>
@@ -24784,7 +24787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="557" hidden="1" spans="1:9">
+    <row r="557" spans="1:9">
       <c r="A557" s="8">
         <v>5</v>
       </c>
@@ -24810,7 +24813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="558" hidden="1" spans="1:9">
+    <row r="558" spans="1:9">
       <c r="A558" s="8">
         <v>6</v>
       </c>
@@ -24836,7 +24839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="559" hidden="1" spans="1:9">
+    <row r="559" spans="1:9">
       <c r="A559" s="8">
         <v>7</v>
       </c>
@@ -24862,7 +24865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="560" hidden="1" spans="1:9">
+    <row r="560" spans="1:9">
       <c r="A560" s="8">
         <v>1</v>
       </c>
@@ -24891,7 +24894,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="561" hidden="1" spans="1:9">
+    <row r="561" spans="1:9">
       <c r="A561" s="8">
         <v>2</v>
       </c>
@@ -24920,7 +24923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="562" hidden="1" spans="1:9">
+    <row r="562" spans="1:9">
       <c r="A562" s="8">
         <v>3</v>
       </c>
@@ -24949,7 +24952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="563" hidden="1" spans="1:9">
+    <row r="563" spans="1:9">
       <c r="A563" s="8">
         <v>4</v>
       </c>
@@ -24975,7 +24978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="564" hidden="1" spans="1:9">
+    <row r="564" spans="1:9">
       <c r="A564" s="8">
         <v>5</v>
       </c>
@@ -25001,7 +25004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="565" hidden="1" spans="1:9">
+    <row r="565" spans="1:9">
       <c r="A565" s="8">
         <v>6</v>
       </c>
@@ -25030,7 +25033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="566" hidden="1" spans="1:9">
+    <row r="566" spans="1:9">
       <c r="A566" s="8">
         <v>7</v>
       </c>
@@ -25056,7 +25059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="567" hidden="1" spans="1:9">
+    <row r="567" spans="1:9">
       <c r="A567" s="8">
         <v>8</v>
       </c>
@@ -25082,7 +25085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="568" hidden="1" spans="1:9">
+    <row r="568" spans="1:9">
       <c r="A568" s="8">
         <v>9</v>
       </c>
@@ -25108,7 +25111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="569" hidden="1" spans="1:9">
+    <row r="569" spans="1:9">
       <c r="A569" s="8">
         <v>10</v>
       </c>
@@ -25134,7 +25137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="570" hidden="1" spans="1:9">
+    <row r="570" spans="1:9">
       <c r="A570" s="8">
         <v>11</v>
       </c>
@@ -25160,7 +25163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="571" hidden="1" spans="1:9">
+    <row r="571" spans="1:9">
       <c r="A571" s="8">
         <v>12</v>
       </c>
@@ -25186,7 +25189,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="572" hidden="1" spans="1:9">
+    <row r="572" spans="1:9">
       <c r="A572" s="8">
         <v>1</v>
       </c>
@@ -25215,7 +25218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="573" hidden="1" spans="1:9">
+    <row r="573" spans="1:9">
       <c r="A573" s="8">
         <v>2</v>
       </c>
@@ -25241,7 +25244,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="574" hidden="1" spans="1:9">
+    <row r="574" spans="1:9">
       <c r="A574" s="8">
         <v>3</v>
       </c>
@@ -25267,7 +25270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="575" hidden="1" spans="1:9">
+    <row r="575" spans="1:9">
       <c r="A575" s="8">
         <v>4</v>
       </c>
@@ -25296,7 +25299,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="576" hidden="1" spans="1:9">
+    <row r="576" spans="1:9">
       <c r="A576" s="8">
         <v>5</v>
       </c>
@@ -25322,7 +25325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="577" hidden="1" spans="1:9">
+    <row r="577" spans="1:9">
       <c r="A577" s="8">
         <v>6</v>
       </c>
@@ -25348,7 +25351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="578" hidden="1" spans="1:9">
+    <row r="578" spans="1:9">
       <c r="A578" s="8">
         <v>7</v>
       </c>
@@ -25377,7 +25380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="579" hidden="1" spans="1:9">
+    <row r="579" spans="1:9">
       <c r="A579" s="8">
         <v>8</v>
       </c>
@@ -25403,7 +25406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="580" hidden="1" spans="1:9">
+    <row r="580" spans="1:9">
       <c r="A580" s="8">
         <v>9</v>
       </c>
@@ -25429,7 +25432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="581" hidden="1" spans="1:9">
+    <row r="581" spans="1:9">
       <c r="A581" s="8">
         <v>10</v>
       </c>
@@ -25455,7 +25458,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="582" hidden="1" spans="1:9">
+    <row r="582" spans="1:9">
       <c r="A582" s="8">
         <v>11</v>
       </c>
@@ -25481,7 +25484,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="583" hidden="1" spans="1:9">
+    <row r="583" spans="1:9">
       <c r="A583" s="8">
         <v>12</v>
       </c>
@@ -25507,7 +25510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="584" hidden="1" spans="1:9">
+    <row r="584" spans="1:9">
       <c r="A584" s="8">
         <v>13</v>
       </c>
@@ -25536,7 +25539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="585" hidden="1" spans="1:9">
+    <row r="585" spans="1:9">
       <c r="A585" s="8">
         <v>14</v>
       </c>
@@ -25562,7 +25565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="586" hidden="1" spans="1:9">
+    <row r="586" spans="1:9">
       <c r="A586" s="8">
         <v>15</v>
       </c>
@@ -25588,7 +25591,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="587" hidden="1" spans="1:9">
+    <row r="587" spans="1:9">
       <c r="A587" s="8">
         <v>16</v>
       </c>
@@ -25614,7 +25617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="588" hidden="1" spans="1:9">
+    <row r="588" spans="1:9">
       <c r="A588" s="8">
         <v>17</v>
       </c>
@@ -25640,7 +25643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="589" hidden="1" spans="1:9">
+    <row r="589" spans="1:9">
       <c r="A589" s="8">
         <v>18</v>
       </c>
@@ -25666,7 +25669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="590" hidden="1" spans="1:9">
+    <row r="590" spans="1:9">
       <c r="A590" s="8">
         <v>19</v>
       </c>
@@ -25692,7 +25695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="591" hidden="1" spans="1:9">
+    <row r="591" spans="1:9">
       <c r="A591" s="8">
         <v>20</v>
       </c>
@@ -25718,7 +25721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="592" hidden="1" spans="1:9">
+    <row r="592" spans="1:9">
       <c r="A592" s="8">
         <v>21</v>
       </c>
@@ -25747,7 +25750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="593" hidden="1" spans="1:9">
+    <row r="593" spans="1:9">
       <c r="A593" s="8">
         <v>1</v>
       </c>
@@ -25773,7 +25776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="594" hidden="1" spans="1:9">
+    <row r="594" spans="1:9">
       <c r="A594" s="8">
         <v>2</v>
       </c>
@@ -25799,7 +25802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="595" hidden="1" spans="1:9">
+    <row r="595" spans="1:9">
       <c r="A595" s="8">
         <v>3</v>
       </c>
@@ -25825,7 +25828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="596" hidden="1" spans="1:9">
+    <row r="596" spans="1:9">
       <c r="A596" s="8">
         <v>4</v>
       </c>
@@ -25854,7 +25857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="597" hidden="1" spans="1:9">
+    <row r="597" spans="1:9">
       <c r="A597" s="8">
         <v>4</v>
       </c>
@@ -25883,7 +25886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="598" hidden="1" spans="1:9">
+    <row r="598" spans="1:9">
       <c r="A598" s="8">
         <v>6</v>
       </c>
@@ -25912,7 +25915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="599" hidden="1" spans="1:9">
+    <row r="599" spans="1:9">
       <c r="A599" s="8">
         <v>7</v>
       </c>
@@ -25941,7 +25944,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="600" hidden="1" spans="1:9">
+    <row r="600" spans="1:9">
       <c r="A600" s="8">
         <v>8</v>
       </c>
@@ -25970,7 +25973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="601" hidden="1" spans="1:9">
+    <row r="601" spans="1:9">
       <c r="A601" s="8">
         <v>9</v>
       </c>
@@ -25999,7 +26002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="602" hidden="1" spans="1:9">
+    <row r="602" spans="1:9">
       <c r="A602" s="8">
         <v>10</v>
       </c>
@@ -26025,7 +26028,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="603" hidden="1" spans="1:9">
+    <row r="603" spans="1:9">
       <c r="A603" s="8">
         <v>10</v>
       </c>
@@ -26054,7 +26057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="604" hidden="1" spans="1:9">
+    <row r="604" spans="1:9">
       <c r="A604" s="8">
         <v>12</v>
       </c>
@@ -26083,7 +26086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="605" hidden="1" spans="1:9">
+    <row r="605" spans="1:9">
       <c r="A605" s="8">
         <v>13</v>
       </c>
@@ -26112,7 +26115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="606" hidden="1" spans="1:9">
+    <row r="606" spans="1:9">
       <c r="A606" s="8" t="s">
         <v>83</v>
       </c>
@@ -26138,7 +26141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="607" hidden="1" spans="1:9">
+    <row r="607" spans="1:9">
       <c r="A607" s="8">
         <v>1</v>
       </c>
@@ -26167,7 +26170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="608" hidden="1" spans="1:9">
+    <row r="608" spans="1:9">
       <c r="A608" s="8">
         <v>2</v>
       </c>
@@ -26196,7 +26199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="609" hidden="1" spans="1:9">
+    <row r="609" spans="1:9">
       <c r="A609" s="8">
         <v>3</v>
       </c>
@@ -26225,7 +26228,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="610" hidden="1" spans="1:9">
+    <row r="610" spans="1:9">
       <c r="A610" s="8">
         <v>3</v>
       </c>
@@ -26254,7 +26257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="611" hidden="1" spans="1:9">
+    <row r="611" spans="1:9">
       <c r="A611" s="8">
         <v>5</v>
       </c>
@@ -26283,7 +26286,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="612" hidden="1" spans="1:9">
+    <row r="612" spans="1:9">
       <c r="A612" s="8">
         <v>6</v>
       </c>
@@ -26309,7 +26312,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="613" hidden="1" spans="1:9">
+    <row r="613" spans="1:9">
       <c r="A613" s="8">
         <v>7</v>
       </c>
@@ -26338,7 +26341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="614" hidden="1" spans="1:9">
+    <row r="614" spans="1:9">
       <c r="A614" s="8">
         <v>8</v>
       </c>
@@ -26364,7 +26367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="615" hidden="1" spans="1:9">
+    <row r="615" spans="1:9">
       <c r="A615" s="8">
         <v>9</v>
       </c>
@@ -26390,7 +26393,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="616" hidden="1" spans="1:9">
+    <row r="616" spans="1:9">
       <c r="A616" s="8">
         <v>10</v>
       </c>
@@ -26416,7 +26419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="617" hidden="1" spans="1:9">
+    <row r="617" spans="1:9">
       <c r="A617" s="8">
         <v>11</v>
       </c>
@@ -26442,7 +26445,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="618" hidden="1" spans="1:9">
+    <row r="618" spans="1:9">
       <c r="A618" s="8">
         <v>12</v>
       </c>
@@ -26468,7 +26471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="619" hidden="1" spans="1:9">
+    <row r="619" spans="1:9">
       <c r="A619" s="8">
         <v>1</v>
       </c>
@@ -26494,7 +26497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="620" hidden="1" spans="1:9">
+    <row r="620" spans="1:9">
       <c r="A620" s="8">
         <v>2</v>
       </c>
@@ -26520,7 +26523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="621" hidden="1" spans="1:9">
+    <row r="621" spans="1:9">
       <c r="A621" s="8">
         <v>3</v>
       </c>
@@ -26546,7 +26549,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="622" hidden="1" spans="1:9">
+    <row r="622" spans="1:9">
       <c r="A622" s="8">
         <v>4</v>
       </c>
@@ -26572,7 +26575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="623" hidden="1" spans="1:9">
+    <row r="623" spans="1:9">
       <c r="A623" s="8">
         <v>5</v>
       </c>
@@ -26598,7 +26601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="624" hidden="1" spans="1:9">
+    <row r="624" spans="1:9">
       <c r="A624" s="8">
         <v>6</v>
       </c>
@@ -26624,7 +26627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="625" hidden="1" spans="1:9">
+    <row r="625" spans="1:9">
       <c r="A625" s="8">
         <v>7</v>
       </c>
@@ -26650,7 +26653,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="626" hidden="1" spans="1:9">
+    <row r="626" spans="1:9">
       <c r="A626" s="8">
         <v>8</v>
       </c>
@@ -26676,7 +26679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="627" hidden="1" spans="1:9">
+    <row r="627" spans="1:9">
       <c r="A627" s="8">
         <v>1</v>
       </c>
@@ -26705,7 +26708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="628" hidden="1" spans="1:9">
+    <row r="628" spans="1:9">
       <c r="A628" s="8">
         <v>2</v>
       </c>
@@ -26734,7 +26737,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="629" hidden="1" spans="1:9">
+    <row r="629" spans="1:9">
       <c r="A629" s="8">
         <v>3</v>
       </c>
@@ -26763,7 +26766,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="630" hidden="1" spans="1:9">
+    <row r="630" spans="1:9">
       <c r="A630" s="8">
         <v>4</v>
       </c>
@@ -26792,7 +26795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="631" hidden="1" spans="1:9">
+    <row r="631" spans="1:9">
       <c r="A631" s="8">
         <v>5</v>
       </c>
@@ -26821,7 +26824,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="632" hidden="1" spans="1:9">
+    <row r="632" spans="1:9">
       <c r="A632" s="8">
         <v>6</v>
       </c>
@@ -26847,7 +26850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="633" hidden="1" spans="1:9">
+    <row r="633" spans="1:9">
       <c r="A633" s="8">
         <v>7</v>
       </c>
@@ -26873,7 +26876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="634" hidden="1" spans="1:9">
+    <row r="634" spans="1:9">
       <c r="A634" s="8">
         <v>8</v>
       </c>
@@ -26899,7 +26902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="635" hidden="1" spans="1:9">
+    <row r="635" spans="1:9">
       <c r="A635" s="8">
         <v>1</v>
       </c>
@@ -26928,7 +26931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="636" hidden="1" spans="1:9">
+    <row r="636" spans="1:9">
       <c r="A636" s="8">
         <v>2</v>
       </c>
@@ -26957,7 +26960,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="637" hidden="1" spans="1:9">
+    <row r="637" spans="1:9">
       <c r="A637" s="8">
         <v>3</v>
       </c>
@@ -26986,7 +26989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="638" hidden="1" spans="1:9">
+    <row r="638" spans="1:9">
       <c r="A638" s="8">
         <v>4</v>
       </c>
@@ -27015,7 +27018,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="639" hidden="1" spans="1:9">
+    <row r="639" spans="1:9">
       <c r="A639" s="8">
         <v>5</v>
       </c>
@@ -27044,7 +27047,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="640" hidden="1" spans="1:9">
+    <row r="640" spans="1:9">
       <c r="A640" s="8">
         <v>6</v>
       </c>
@@ -27070,7 +27073,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="641" hidden="1" spans="1:9">
+    <row r="641" spans="1:9">
       <c r="A641" s="8">
         <v>7</v>
       </c>
@@ -27099,7 +27102,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="642" hidden="1" spans="1:9">
+    <row r="642" spans="1:9">
       <c r="A642" s="8">
         <v>7</v>
       </c>
@@ -27128,7 +27131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="643" hidden="1" spans="1:9">
+    <row r="643" spans="1:9">
       <c r="A643" s="8">
         <v>9</v>
       </c>
@@ -27157,7 +27160,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="644" hidden="1" spans="1:9">
+    <row r="644" spans="1:9">
       <c r="A644" s="8">
         <v>10</v>
       </c>
@@ -27183,7 +27186,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="645" hidden="1" spans="1:9">
+    <row r="645" spans="1:9">
       <c r="A645" s="8">
         <v>11</v>
       </c>
@@ -27209,7 +27212,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="646" hidden="1" spans="1:9">
+    <row r="646" spans="1:9">
       <c r="A646" s="8">
         <v>12</v>
       </c>
@@ -27235,7 +27238,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="647" hidden="1" spans="1:9">
+    <row r="647" spans="1:9">
       <c r="A647" s="8">
         <v>13</v>
       </c>
@@ -27261,7 +27264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="648" hidden="1" spans="1:9">
+    <row r="648" spans="1:9">
       <c r="A648" s="8">
         <v>14</v>
       </c>
@@ -27287,7 +27290,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="649" hidden="1" spans="1:9">
+    <row r="649" spans="1:9">
       <c r="A649" s="8">
         <v>15</v>
       </c>
@@ -27313,7 +27316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="650" hidden="1" spans="1:9">
+    <row r="650" spans="1:9">
       <c r="A650" s="8">
         <v>16</v>
       </c>
@@ -27339,7 +27342,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="651" hidden="1" spans="1:9">
+    <row r="651" spans="1:9">
       <c r="A651" s="8">
         <v>17</v>
       </c>
@@ -27365,7 +27368,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="652" hidden="1" spans="1:9">
+    <row r="652" spans="1:9">
       <c r="A652" s="8">
         <v>18</v>
       </c>
@@ -27391,7 +27394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="653" hidden="1" spans="1:9">
+    <row r="653" spans="1:9">
       <c r="A653" s="8">
         <v>19</v>
       </c>
@@ -27417,7 +27420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="654" hidden="1" spans="1:9">
+    <row r="654" spans="1:9">
       <c r="A654" s="8" t="s">
         <v>83</v>
       </c>
@@ -27443,7 +27446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="655" hidden="1" spans="1:9">
+    <row r="655" spans="1:9">
       <c r="A655" s="8" t="s">
         <v>83</v>
       </c>
@@ -27469,7 +27472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="656" hidden="1" spans="1:9">
+    <row r="656" spans="1:9">
       <c r="A656" s="8" t="s">
         <v>83</v>
       </c>
@@ -27495,7 +27498,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="657" hidden="1" spans="1:9">
+    <row r="657" spans="1:9">
       <c r="A657" s="8" t="s">
         <v>83</v>
       </c>
@@ -27521,7 +27524,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="658" hidden="1" spans="1:9">
+    <row r="658" spans="1:9">
       <c r="A658" s="8" t="s">
         <v>83</v>
       </c>
@@ -27547,7 +27550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="659" hidden="1" spans="1:9">
+    <row r="659" spans="1:9">
       <c r="A659" s="8" t="s">
         <v>83</v>
       </c>
@@ -27573,7 +27576,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="660" hidden="1" spans="1:9">
+    <row r="660" spans="1:9">
       <c r="A660" s="8" t="s">
         <v>83</v>
       </c>
@@ -27599,7 +27602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="661" hidden="1" spans="1:9">
+    <row r="661" spans="1:9">
       <c r="A661" s="8">
         <v>1</v>
       </c>
@@ -27625,7 +27628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="662" hidden="1" spans="1:9">
+    <row r="662" spans="1:9">
       <c r="A662" s="8">
         <v>2</v>
       </c>
@@ -27654,7 +27657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="663" hidden="1" spans="1:9">
+    <row r="663" spans="1:9">
       <c r="A663" s="8">
         <v>3</v>
       </c>
@@ -27680,7 +27683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="664" hidden="1" spans="1:9">
+    <row r="664" spans="1:9">
       <c r="A664" s="8">
         <v>4</v>
       </c>
@@ -27706,7 +27709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="665" hidden="1" spans="1:9">
+    <row r="665" spans="1:9">
       <c r="A665" s="8">
         <v>5</v>
       </c>
@@ -27732,7 +27735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="666" hidden="1" spans="1:9">
+    <row r="666" spans="1:9">
       <c r="A666" s="8">
         <v>6</v>
       </c>
@@ -27758,7 +27761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="667" hidden="1" spans="1:9">
+    <row r="667" spans="1:9">
       <c r="A667" s="8">
         <v>7</v>
       </c>
@@ -27784,7 +27787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="668" hidden="1" spans="1:9">
+    <row r="668" spans="1:9">
       <c r="A668" s="8">
         <v>8</v>
       </c>
@@ -27810,7 +27813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="669" hidden="1" spans="1:9">
+    <row r="669" spans="1:9">
       <c r="A669" s="8">
         <v>1</v>
       </c>
@@ -27839,7 +27842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="670" hidden="1" spans="1:9">
+    <row r="670" spans="1:9">
       <c r="A670" s="8">
         <v>2</v>
       </c>
@@ -27865,7 +27868,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="671" hidden="1" spans="1:9">
+    <row r="671" spans="1:9">
       <c r="A671" s="8">
         <v>3</v>
       </c>
@@ -27894,7 +27897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="672" hidden="1" spans="1:9">
+    <row r="672" spans="1:9">
       <c r="A672" s="8">
         <v>4</v>
       </c>
@@ -27920,7 +27923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="673" hidden="1" spans="1:9">
+    <row r="673" spans="1:9">
       <c r="A673" s="8">
         <v>5</v>
       </c>
@@ -27949,7 +27952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="674" hidden="1" spans="1:9">
+    <row r="674" spans="1:9">
       <c r="A674" s="8">
         <v>6</v>
       </c>
@@ -27975,7 +27978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="675" hidden="1" spans="1:9">
+    <row r="675" spans="1:9">
       <c r="A675" s="8">
         <v>7</v>
       </c>
@@ -28001,7 +28004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="676" hidden="1" spans="1:9">
+    <row r="676" spans="1:9">
       <c r="A676" s="8">
         <v>8</v>
       </c>
@@ -28027,7 +28030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="677" hidden="1" spans="1:9">
+    <row r="677" spans="1:9">
       <c r="A677" s="8">
         <v>1</v>
       </c>
@@ -28056,7 +28059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="678" hidden="1" spans="1:9">
+    <row r="678" spans="1:9">
       <c r="A678" s="8">
         <v>2</v>
       </c>
@@ -28085,7 +28088,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="679" hidden="1" spans="1:9">
+    <row r="679" spans="1:9">
       <c r="A679" s="8">
         <v>3</v>
       </c>
@@ -28114,7 +28117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="680" hidden="1" spans="1:9">
+    <row r="680" spans="1:9">
       <c r="A680" s="8">
         <v>4</v>
       </c>
@@ -28140,7 +28143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="681" hidden="1" spans="1:9">
+    <row r="681" spans="1:9">
       <c r="A681" s="8">
         <v>5</v>
       </c>
@@ -28166,7 +28169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="682" hidden="1" spans="1:9">
+    <row r="682" spans="1:9">
       <c r="A682" s="8">
         <v>6</v>
       </c>
@@ -28192,7 +28195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="683" hidden="1" spans="1:9">
+    <row r="683" spans="1:9">
       <c r="A683" s="8">
         <v>7</v>
       </c>
@@ -28218,7 +28221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="684" hidden="1" spans="1:9">
+    <row r="684" spans="1:9">
       <c r="A684" s="8">
         <v>8</v>
       </c>
@@ -28247,7 +28250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="685" hidden="1" spans="1:9">
+    <row r="685" spans="1:9">
       <c r="A685" s="8">
         <v>9</v>
       </c>
@@ -28273,7 +28276,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="686" hidden="1" spans="1:9">
+    <row r="686" spans="1:9">
       <c r="A686" s="8">
         <v>10</v>
       </c>
@@ -28302,7 +28305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="687" hidden="1" spans="1:9">
+    <row r="687" spans="1:9">
       <c r="A687" s="8">
         <v>11</v>
       </c>
@@ -28328,7 +28331,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="688" hidden="1" spans="1:9">
+    <row r="688" spans="1:9">
       <c r="A688" s="8">
         <v>12</v>
       </c>
@@ -28354,7 +28357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="689" hidden="1" spans="1:9">
+    <row r="689" spans="1:9">
       <c r="A689" s="8">
         <v>1</v>
       </c>
@@ -28383,7 +28386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="690" hidden="1" spans="1:9">
+    <row r="690" spans="1:9">
       <c r="A690" s="8">
         <v>2</v>
       </c>
@@ -28412,7 +28415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="691" hidden="1" spans="1:9">
+    <row r="691" spans="1:9">
       <c r="A691" s="8">
         <v>3</v>
       </c>
@@ -28441,7 +28444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="692" hidden="1" spans="1:9">
+    <row r="692" spans="1:9">
       <c r="A692" s="8">
         <v>4</v>
       </c>
@@ -28467,7 +28470,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="693" hidden="1" spans="1:9">
+    <row r="693" spans="1:9">
       <c r="A693" s="8">
         <v>5</v>
       </c>
@@ -28493,7 +28496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="694" hidden="1" spans="1:9">
+    <row r="694" spans="1:9">
       <c r="A694" s="8">
         <v>6</v>
       </c>
@@ -28522,7 +28525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="695" hidden="1" spans="1:9">
+    <row r="695" spans="1:9">
       <c r="A695" s="8">
         <v>7</v>
       </c>
@@ -28548,7 +28551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="696" hidden="1" spans="1:9">
+    <row r="696" spans="1:9">
       <c r="A696" s="8">
         <v>8</v>
       </c>
@@ -28577,7 +28580,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="697" hidden="1" spans="1:9">
+    <row r="697" spans="1:9">
       <c r="A697" s="8">
         <v>9</v>
       </c>
@@ -28606,7 +28609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="698" hidden="1" spans="1:9">
+    <row r="698" spans="1:9">
       <c r="A698" s="8">
         <v>10</v>
       </c>
@@ -28632,7 +28635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="699" hidden="1" spans="1:9">
+    <row r="699" spans="1:9">
       <c r="A699" s="8">
         <v>11</v>
       </c>
@@ -28658,7 +28661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="700" hidden="1" spans="1:9">
+    <row r="700" spans="1:9">
       <c r="A700" s="8">
         <v>12</v>
       </c>
@@ -28684,7 +28687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="701" hidden="1" spans="1:9">
+    <row r="701" spans="1:9">
       <c r="A701" s="8">
         <v>13</v>
       </c>
@@ -28710,7 +28713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="702" hidden="1" spans="1:9">
+    <row r="702" spans="1:9">
       <c r="A702" s="8">
         <v>14</v>
       </c>
@@ -28739,7 +28742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="703" hidden="1" spans="1:9">
+    <row r="703" spans="1:9">
       <c r="A703" s="8">
         <v>15</v>
       </c>
@@ -28765,7 +28768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="704" hidden="1" spans="1:9">
+    <row r="704" spans="1:9">
       <c r="A704" s="8" t="s">
         <v>83</v>
       </c>
@@ -28791,7 +28794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="705" hidden="1" spans="1:9">
+    <row r="705" spans="1:9">
       <c r="A705" s="8" t="s">
         <v>83</v>
       </c>
@@ -28817,7 +28820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="706" hidden="1" spans="1:9">
+    <row r="706" spans="1:9">
       <c r="A706" s="8">
         <v>1</v>
       </c>
@@ -28846,7 +28849,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="707" hidden="1" spans="1:9">
+    <row r="707" spans="1:9">
       <c r="A707" s="8">
         <v>2</v>
       </c>
@@ -28875,7 +28878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="708" hidden="1" spans="1:9">
+    <row r="708" spans="1:9">
       <c r="A708" s="8">
         <v>3</v>
       </c>
@@ -28904,7 +28907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="709" hidden="1" spans="1:9">
+    <row r="709" spans="1:9">
       <c r="A709" s="8">
         <v>4</v>
       </c>
@@ -28933,7 +28936,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="710" hidden="1" spans="1:9">
+    <row r="710" spans="1:9">
       <c r="A710" s="8">
         <v>5</v>
       </c>
@@ -28959,7 +28962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="711" hidden="1" spans="1:9">
+    <row r="711" spans="1:9">
       <c r="A711" s="8">
         <v>6</v>
       </c>
@@ -28985,7 +28988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="712" hidden="1" spans="1:9">
+    <row r="712" spans="1:9">
       <c r="A712" s="8">
         <v>7</v>
       </c>
@@ -29011,7 +29014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="713" hidden="1" spans="1:9">
+    <row r="713" spans="1:9">
       <c r="A713" s="8">
         <v>8</v>
       </c>
@@ -29037,7 +29040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="714" hidden="1" spans="1:9">
+    <row r="714" spans="1:9">
       <c r="A714" s="8">
         <v>9</v>
       </c>
@@ -29063,7 +29066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="715" hidden="1" spans="1:9">
+    <row r="715" spans="1:9">
       <c r="A715" s="8">
         <v>10</v>
       </c>
@@ -29089,7 +29092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="716" hidden="1" spans="1:9">
+    <row r="716" spans="1:9">
       <c r="A716" s="8">
         <v>11</v>
       </c>
@@ -29115,7 +29118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="717" hidden="1" spans="1:9">
+    <row r="717" spans="1:9">
       <c r="A717" s="8">
         <v>12</v>
       </c>
@@ -29141,7 +29144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="718" hidden="1" spans="1:9">
+    <row r="718" spans="1:9">
       <c r="A718" s="8" t="s">
         <v>83</v>
       </c>
@@ -29167,7 +29170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="719" hidden="1" spans="1:9">
+    <row r="719" spans="1:9">
       <c r="A719" s="8" t="s">
         <v>83</v>
       </c>
@@ -29193,7 +29196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="720" hidden="1" spans="1:9">
+    <row r="720" spans="1:9">
       <c r="A720" s="8">
         <v>1</v>
       </c>
@@ -29219,7 +29222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="721" hidden="1" spans="1:9">
+    <row r="721" spans="1:9">
       <c r="A721" s="8">
         <v>2</v>
       </c>
@@ -29248,7 +29251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="722" hidden="1" spans="1:9">
+    <row r="722" spans="1:9">
       <c r="A722" s="8">
         <v>3</v>
       </c>
@@ -29277,7 +29280,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="723" hidden="1" spans="1:9">
+    <row r="723" spans="1:9">
       <c r="A723" s="8">
         <v>4</v>
       </c>
@@ -29303,7 +29306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="724" hidden="1" spans="1:9">
+    <row r="724" spans="1:9">
       <c r="A724" s="8">
         <v>5</v>
       </c>
@@ -29329,7 +29332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="725" hidden="1" spans="1:9">
+    <row r="725" spans="1:9">
       <c r="A725" s="8">
         <v>6</v>
       </c>
@@ -29355,7 +29358,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="726" hidden="1" spans="1:9">
+    <row r="726" spans="1:9">
       <c r="A726" s="8">
         <v>7</v>
       </c>
@@ -29381,7 +29384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="727" hidden="1" spans="1:9">
+    <row r="727" spans="1:9">
       <c r="A727" s="8">
         <v>8</v>
       </c>
@@ -29407,7 +29410,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="728" hidden="1" spans="1:9">
+    <row r="728" spans="1:9">
       <c r="A728" s="8">
         <v>9</v>
       </c>
@@ -29433,7 +29436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="729" hidden="1" spans="1:9">
+    <row r="729" spans="1:9">
       <c r="A729" s="8">
         <v>10</v>
       </c>
@@ -29459,7 +29462,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="730" hidden="1" spans="1:9">
+    <row r="730" spans="1:9">
       <c r="A730" s="8" t="s">
         <v>83</v>
       </c>
@@ -29485,7 +29488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="731" hidden="1" spans="1:9">
+    <row r="731" spans="1:9">
       <c r="A731" s="8" t="s">
         <v>83</v>
       </c>
@@ -29511,7 +29514,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="732" hidden="1" spans="1:9">
+    <row r="732" spans="1:9">
       <c r="A732" s="8">
         <v>1</v>
       </c>
@@ -29540,7 +29543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="733" hidden="1" spans="1:9">
+    <row r="733" spans="1:9">
       <c r="A733" s="8">
         <v>2</v>
       </c>
@@ -29566,7 +29569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="734" hidden="1" spans="1:9">
+    <row r="734" spans="1:9">
       <c r="A734" s="8">
         <v>3</v>
       </c>
@@ -29592,7 +29595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="735" hidden="1" spans="1:9">
+    <row r="735" spans="1:9">
       <c r="A735" s="8">
         <v>4</v>
       </c>
@@ -29621,7 +29624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="736" hidden="1" spans="1:9">
+    <row r="736" spans="1:9">
       <c r="A736" s="8">
         <v>5</v>
       </c>
@@ -29650,7 +29653,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="737" hidden="1" spans="1:9">
+    <row r="737" spans="1:9">
       <c r="A737" s="8">
         <v>6</v>
       </c>
@@ -29676,7 +29679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="738" hidden="1" spans="1:9">
+    <row r="738" spans="1:9">
       <c r="A738" s="8">
         <v>7</v>
       </c>
@@ -29702,7 +29705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="739" hidden="1" spans="1:9">
+    <row r="739" spans="1:9">
       <c r="A739" s="8">
         <v>8</v>
       </c>
@@ -29728,7 +29731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="740" hidden="1" spans="1:9">
+    <row r="740" spans="1:9">
       <c r="A740" s="8">
         <v>9</v>
       </c>
@@ -29757,7 +29760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="741" hidden="1" spans="1:9">
+    <row r="741" spans="1:9">
       <c r="A741" s="8">
         <v>10</v>
       </c>
@@ -29783,7 +29786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="742" hidden="1" spans="1:9">
+    <row r="742" spans="1:9">
       <c r="A742" s="8">
         <v>11</v>
       </c>
@@ -29809,7 +29812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="743" hidden="1" spans="1:9">
+    <row r="743" spans="1:9">
       <c r="A743" s="8">
         <v>12</v>
       </c>
@@ -29835,7 +29838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="744" hidden="1" spans="1:9">
+    <row r="744" spans="1:9">
       <c r="A744" s="8">
         <v>13</v>
       </c>
@@ -29864,7 +29867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="745" hidden="1" spans="1:9">
+    <row r="745" spans="1:9">
       <c r="A745" s="8">
         <v>14</v>
       </c>
@@ -29890,7 +29893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="746" hidden="1" spans="1:9">
+    <row r="746" spans="1:9">
       <c r="A746" s="8">
         <v>15</v>
       </c>
@@ -29919,7 +29922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="747" hidden="1" spans="1:9">
+    <row r="747" spans="1:9">
       <c r="A747" s="8">
         <v>16</v>
       </c>
@@ -29945,7 +29948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="748" hidden="1" spans="1:9">
+    <row r="748" spans="1:9">
       <c r="A748" s="8">
         <v>17</v>
       </c>
@@ -29971,7 +29974,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="749" hidden="1" spans="1:9">
+    <row r="749" spans="1:9">
       <c r="A749" s="8">
         <v>18</v>
       </c>
@@ -29997,7 +30000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="750" hidden="1" spans="1:9">
+    <row r="750" spans="1:9">
       <c r="A750" s="8">
         <v>19</v>
       </c>
@@ -30023,7 +30026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="751" hidden="1" spans="1:9">
+    <row r="751" spans="1:9">
       <c r="A751" s="8">
         <v>20</v>
       </c>
@@ -30049,7 +30052,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="752" hidden="1" spans="1:9">
+    <row r="752" spans="1:9">
       <c r="A752" s="8">
         <v>21</v>
       </c>
@@ -30075,7 +30078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="753" hidden="1" spans="1:9">
+    <row r="753" spans="1:9">
       <c r="A753" s="8">
         <v>22</v>
       </c>
@@ -30101,7 +30104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="754" hidden="1" spans="1:9">
+    <row r="754" spans="1:9">
       <c r="A754" s="8">
         <v>23</v>
       </c>
@@ -30127,7 +30130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="755" hidden="1" spans="1:9">
+    <row r="755" spans="1:9">
       <c r="A755" s="8">
         <v>1</v>
       </c>
@@ -30156,7 +30159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="756" hidden="1" spans="1:9">
+    <row r="756" spans="1:9">
       <c r="A756" s="8">
         <v>2</v>
       </c>
@@ -30185,7 +30188,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="757" hidden="1" spans="1:9">
+    <row r="757" spans="1:9">
       <c r="A757" s="8">
         <v>3</v>
       </c>
@@ -30214,7 +30217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="758" hidden="1" spans="1:9">
+    <row r="758" spans="1:9">
       <c r="A758" s="8">
         <v>4</v>
       </c>
@@ -30243,7 +30246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="759" hidden="1" spans="1:9">
+    <row r="759" spans="1:9">
       <c r="A759" s="8">
         <v>5</v>
       </c>
@@ -30272,7 +30275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="760" hidden="1" spans="1:9">
+    <row r="760" spans="1:9">
       <c r="A760" s="8">
         <v>6</v>
       </c>
@@ -30301,7 +30304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="761" hidden="1" spans="1:9">
+    <row r="761" spans="1:9">
       <c r="A761" s="8">
         <v>7</v>
       </c>
@@ -30330,7 +30333,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="762" hidden="1" spans="1:9">
+    <row r="762" spans="1:9">
       <c r="A762" s="8">
         <v>8</v>
       </c>
@@ -30359,7 +30362,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="763" hidden="1" spans="1:9">
+    <row r="763" spans="1:9">
       <c r="A763" s="8">
         <v>9</v>
       </c>
@@ -30388,7 +30391,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="764" hidden="1" spans="1:9">
+    <row r="764" spans="1:9">
       <c r="A764" s="8">
         <v>10</v>
       </c>
@@ -30417,7 +30420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="765" hidden="1" spans="1:9">
+    <row r="765" spans="1:9">
       <c r="A765" s="8">
         <v>11</v>
       </c>
@@ -30443,7 +30446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="766" hidden="1" spans="1:9">
+    <row r="766" spans="1:9">
       <c r="A766" s="8">
         <v>12</v>
       </c>
@@ -30472,7 +30475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="767" hidden="1" spans="1:9">
+    <row r="767" spans="1:9">
       <c r="A767" s="8">
         <v>13</v>
       </c>
@@ -30498,7 +30501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="768" hidden="1" spans="1:9">
+    <row r="768" spans="1:9">
       <c r="A768" s="8">
         <v>14</v>
       </c>
@@ -30527,7 +30530,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="769" hidden="1" spans="1:9">
+    <row r="769" spans="1:9">
       <c r="A769" s="8">
         <v>15</v>
       </c>
@@ -30553,7 +30556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="770" hidden="1" spans="1:9">
+    <row r="770" spans="1:9">
       <c r="A770" s="8">
         <v>16</v>
       </c>
@@ -30579,7 +30582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="771" hidden="1" spans="1:9">
+    <row r="771" spans="1:9">
       <c r="A771" s="8">
         <v>17</v>
       </c>
@@ -30608,7 +30611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="772" hidden="1" spans="1:9">
+    <row r="772" spans="1:9">
       <c r="A772" s="8">
         <v>18</v>
       </c>
@@ -30637,7 +30640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="773" hidden="1" spans="1:9">
+    <row r="773" spans="1:9">
       <c r="A773" s="8">
         <v>19</v>
       </c>
@@ -30663,7 +30666,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="774" hidden="1" spans="1:9">
+    <row r="774" spans="1:9">
       <c r="A774" s="8">
         <v>20</v>
       </c>
@@ -30689,7 +30692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="775" hidden="1" spans="1:9">
+    <row r="775" spans="1:9">
       <c r="A775" s="8">
         <v>21</v>
       </c>
@@ -30715,7 +30718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="776" hidden="1" spans="1:9">
+    <row r="776" spans="1:9">
       <c r="A776" s="8">
         <v>22</v>
       </c>
@@ -30741,7 +30744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="777" hidden="1" spans="1:9">
+    <row r="777" spans="1:9">
       <c r="A777" s="8">
         <v>23</v>
       </c>
@@ -30767,7 +30770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="778" hidden="1" spans="1:9">
+    <row r="778" spans="1:9">
       <c r="A778" s="8">
         <v>24</v>
       </c>
@@ -30793,7 +30796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="779" hidden="1" spans="1:9">
+    <row r="779" spans="1:9">
       <c r="A779" s="8">
         <v>25</v>
       </c>
@@ -30819,7 +30822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="780" hidden="1" spans="1:9">
+    <row r="780" spans="1:9">
       <c r="A780" s="8">
         <v>26</v>
       </c>
@@ -30845,7 +30848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="781" hidden="1" spans="1:9">
+    <row r="781" spans="1:9">
       <c r="A781" s="8">
         <v>27</v>
       </c>
@@ -30871,7 +30874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="782" hidden="1" spans="1:9">
+    <row r="782" spans="1:9">
       <c r="A782" s="8">
         <v>28</v>
       </c>
@@ -30897,7 +30900,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="783" hidden="1" spans="1:9">
+    <row r="783" spans="1:9">
       <c r="A783" s="8">
         <v>29</v>
       </c>
@@ -30923,7 +30926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="784" hidden="1" spans="1:9">
+    <row r="784" spans="1:9">
       <c r="A784" s="8">
         <v>30</v>
       </c>
@@ -30949,7 +30952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="785" hidden="1" spans="1:9">
+    <row r="785" spans="1:9">
       <c r="A785" s="8">
         <v>31</v>
       </c>
@@ -30975,7 +30978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="786" hidden="1" spans="1:9">
+    <row r="786" spans="1:9">
       <c r="A786" s="8" t="s">
         <v>83</v>
       </c>
@@ -31001,7 +31004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="787" hidden="1" spans="1:9">
+    <row r="787" spans="1:9">
       <c r="A787" s="8">
         <v>1</v>
       </c>
@@ -31030,7 +31033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="788" hidden="1" spans="1:9">
+    <row r="788" spans="1:9">
       <c r="A788" s="8">
         <v>2</v>
       </c>
@@ -31050,15 +31053,15 @@
         <v>1426</v>
       </c>
       <c r="G788" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I788" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="789" hidden="1" spans="1:9">
+    <row r="789" spans="1:9">
       <c r="A789" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B789" s="8" t="s">
         <v>9</v>
@@ -31082,9 +31085,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="790" hidden="1" spans="1:9">
+    <row r="790" spans="1:9">
       <c r="A790" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B790" s="8" t="s">
         <v>9</v>
@@ -31102,13 +31105,13 @@
         <v>1426</v>
       </c>
       <c r="G790" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I790" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="791" hidden="1" spans="1:9">
+    <row r="791" spans="1:9">
       <c r="A791" s="8">
         <v>5</v>
       </c>
@@ -31128,15 +31131,15 @@
         <v>1430</v>
       </c>
       <c r="G791" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I791" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="792" hidden="1" spans="1:9">
+    <row r="792" spans="1:9">
       <c r="A792" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B792" s="8" t="s">
         <v>9</v>
@@ -31154,15 +31157,15 @@
         <v>1430</v>
       </c>
       <c r="G792" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I792" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="793" hidden="1" spans="1:9">
+    <row r="793" spans="1:9">
       <c r="A793" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B793" s="8" t="s">
         <v>9</v>
@@ -31186,9 +31189,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="794" hidden="1" spans="1:9">
+    <row r="794" spans="1:9">
       <c r="A794" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B794" s="8" t="s">
         <v>9</v>
@@ -31206,15 +31209,15 @@
         <v>1430</v>
       </c>
       <c r="G794" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I794" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="795" hidden="1" spans="1:9">
+    <row r="795" spans="1:9">
       <c r="A795" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B795" s="8" t="s">
         <v>9</v>
@@ -31232,13 +31235,13 @@
         <v>1430</v>
       </c>
       <c r="G795" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I795" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="796" hidden="1" spans="1:9">
+    <row r="796" spans="1:9">
       <c r="A796" s="8">
         <v>10</v>
       </c>
@@ -31264,7 +31267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="797" hidden="1" spans="1:9">
+    <row r="797" spans="1:9">
       <c r="A797" s="8">
         <v>10</v>
       </c>
@@ -31290,7 +31293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="798" hidden="1" spans="1:9">
+    <row r="798" spans="1:9">
       <c r="A798" s="8">
         <v>10</v>
       </c>
@@ -31316,7 +31319,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="799" hidden="1" spans="1:9">
+    <row r="799" spans="1:9">
       <c r="A799" s="8">
         <v>1</v>
       </c>
@@ -31345,7 +31348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="800" hidden="1" spans="1:9">
+    <row r="800" spans="1:9">
       <c r="A800" s="8">
         <v>2</v>
       </c>
@@ -31374,7 +31377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="801" hidden="1" spans="1:9">
+    <row r="801" spans="1:9">
       <c r="A801" s="8">
         <v>3</v>
       </c>
@@ -31403,7 +31406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="802" hidden="1" spans="1:9">
+    <row r="802" spans="1:9">
       <c r="A802" s="8">
         <v>4</v>
       </c>
@@ -31429,7 +31432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="803" hidden="1" spans="1:9">
+    <row r="803" spans="1:9">
       <c r="A803" s="8">
         <v>5</v>
       </c>
@@ -31455,7 +31458,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="804" hidden="1" spans="1:9">
+    <row r="804" spans="1:9">
       <c r="A804" s="8">
         <v>6</v>
       </c>
@@ -31481,7 +31484,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="805" hidden="1" spans="1:9">
+    <row r="805" spans="1:9">
       <c r="A805" s="8">
         <v>7</v>
       </c>
@@ -31507,7 +31510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="806" hidden="1" spans="1:9">
+    <row r="806" spans="1:9">
       <c r="A806" s="8">
         <v>8</v>
       </c>
@@ -31533,7 +31536,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="807" hidden="1" spans="1:9">
+    <row r="807" spans="1:9">
       <c r="A807" s="8">
         <v>9</v>
       </c>
@@ -31559,7 +31562,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="808" hidden="1" spans="1:9">
+    <row r="808" spans="1:9">
       <c r="A808" s="8">
         <v>10</v>
       </c>
@@ -31588,7 +31591,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="809" hidden="1" spans="1:9">
+    <row r="809" spans="1:9">
       <c r="A809" s="8">
         <v>11</v>
       </c>
@@ -31614,7 +31617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="810" hidden="1" spans="1:9">
+    <row r="810" spans="1:9">
       <c r="A810" s="8">
         <v>12</v>
       </c>
@@ -31640,7 +31643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="811" hidden="1" spans="1:9">
+    <row r="811" spans="1:9">
       <c r="A811" s="8">
         <v>13</v>
       </c>
@@ -31666,7 +31669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="812" hidden="1" spans="1:9">
+    <row r="812" spans="1:9">
       <c r="A812" s="8">
         <v>14</v>
       </c>
@@ -31692,7 +31695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="813" hidden="1" spans="1:9">
+    <row r="813" spans="1:9">
       <c r="A813" s="8">
         <v>15</v>
       </c>
@@ -31718,7 +31721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="814" hidden="1" spans="1:9">
+    <row r="814" spans="1:9">
       <c r="A814" s="8">
         <v>16</v>
       </c>
@@ -31744,7 +31747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="815" hidden="1" spans="1:9">
+    <row r="815" spans="1:9">
       <c r="A815" s="8">
         <v>17</v>
       </c>
@@ -31770,7 +31773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="816" hidden="1" spans="1:9">
+    <row r="816" spans="1:9">
       <c r="A816" s="8">
         <v>18</v>
       </c>
@@ -31796,7 +31799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="817" hidden="1" spans="1:9">
+    <row r="817" spans="1:9">
       <c r="A817" s="8">
         <v>19</v>
       </c>
@@ -31822,7 +31825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="818" hidden="1" spans="1:9">
+    <row r="818" spans="1:9">
       <c r="A818" s="8">
         <v>1</v>
       </c>
@@ -31851,7 +31854,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="819" hidden="1" spans="1:9">
+    <row r="819" spans="1:9">
       <c r="A819" s="8">
         <v>2</v>
       </c>
@@ -31880,7 +31883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="820" hidden="1" spans="1:9">
+    <row r="820" spans="1:9">
       <c r="A820" s="8">
         <v>3</v>
       </c>
@@ -31906,7 +31909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="821" hidden="1" spans="1:9">
+    <row r="821" spans="1:9">
       <c r="A821" s="8">
         <v>4</v>
       </c>
@@ -31932,7 +31935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="822" hidden="1" spans="1:9">
+    <row r="822" spans="1:9">
       <c r="A822" s="8">
         <v>5</v>
       </c>
@@ -31958,7 +31961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="823" hidden="1" spans="1:9">
+    <row r="823" spans="1:9">
       <c r="A823" s="8">
         <v>6</v>
       </c>
@@ -31984,7 +31987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="824" hidden="1" spans="1:9">
+    <row r="824" spans="1:9">
       <c r="A824" s="8">
         <v>7</v>
       </c>
@@ -32010,7 +32013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="825" hidden="1" spans="1:9">
+    <row r="825" spans="1:9">
       <c r="A825" s="8">
         <v>8</v>
       </c>
@@ -32036,7 +32039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="826" hidden="1" spans="1:9">
+    <row r="826" spans="1:9">
       <c r="A826" s="8">
         <v>9</v>
       </c>
@@ -32062,7 +32065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="827" hidden="1" spans="1:9">
+    <row r="827" spans="1:9">
       <c r="A827" s="8">
         <v>10</v>
       </c>
@@ -32088,7 +32091,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="828" hidden="1" spans="1:9">
+    <row r="828" spans="1:9">
       <c r="A828" s="8">
         <v>11</v>
       </c>
@@ -32114,7 +32117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="829" hidden="1" spans="1:9">
+    <row r="829" spans="1:9">
       <c r="A829" s="8">
         <v>12</v>
       </c>
@@ -32140,7 +32143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="830" hidden="1" spans="1:9">
+    <row r="830" spans="1:9">
       <c r="A830" s="8">
         <v>13</v>
       </c>
@@ -32166,7 +32169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="831" hidden="1" spans="1:9">
+    <row r="831" spans="1:9">
       <c r="A831" s="8">
         <v>14</v>
       </c>
@@ -32192,7 +32195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="832" hidden="1" spans="1:9">
+    <row r="832" spans="1:9">
       <c r="A832" s="8">
         <v>15</v>
       </c>
@@ -32221,7 +32224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="833" hidden="1" spans="1:9">
+    <row r="833" spans="1:9">
       <c r="A833" s="8">
         <v>16</v>
       </c>
@@ -32247,7 +32250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="834" hidden="1" spans="1:9">
+    <row r="834" spans="1:9">
       <c r="A834" s="8">
         <v>17</v>
       </c>
@@ -32273,7 +32276,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="835" hidden="1" spans="1:9">
+    <row r="835" spans="1:9">
       <c r="A835" s="8">
         <v>18</v>
       </c>
@@ -32299,7 +32302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="836" hidden="1" spans="1:9">
+    <row r="836" spans="1:9">
       <c r="A836" s="8">
         <v>19</v>
       </c>
@@ -32325,7 +32328,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="837" hidden="1" spans="1:9">
+    <row r="837" spans="1:9">
       <c r="A837" s="8">
         <v>20</v>
       </c>
@@ -32351,7 +32354,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="838" hidden="1" spans="1:9">
+    <row r="838" spans="1:9">
       <c r="A838" s="8" t="s">
         <v>83</v>
       </c>
@@ -32377,7 +32380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="839" hidden="1" spans="1:9">
+    <row r="839" spans="1:9">
       <c r="A839" s="8">
         <v>1</v>
       </c>
@@ -32403,7 +32406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="840" hidden="1" spans="1:9">
+    <row r="840" spans="1:9">
       <c r="A840" s="8">
         <v>2</v>
       </c>
@@ -32429,7 +32432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="841" hidden="1" spans="1:9">
+    <row r="841" spans="1:9">
       <c r="A841" s="8">
         <v>3</v>
       </c>
@@ -32455,7 +32458,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="842" hidden="1" spans="1:9">
+    <row r="842" spans="1:9">
       <c r="A842" s="8">
         <v>4</v>
       </c>
@@ -32481,7 +32484,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="843" hidden="1" spans="1:9">
+    <row r="843" spans="1:9">
       <c r="A843" s="8">
         <v>5</v>
       </c>
@@ -32510,7 +32513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="844" hidden="1" spans="1:9">
+    <row r="844" spans="1:9">
       <c r="A844" s="8">
         <v>6</v>
       </c>
@@ -32536,7 +32539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="845" hidden="1" spans="1:9">
+    <row r="845" spans="1:9">
       <c r="A845" s="8">
         <v>7</v>
       </c>
@@ -32562,7 +32565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="846" hidden="1" spans="1:9">
+    <row r="846" spans="1:9">
       <c r="A846" s="8">
         <v>8</v>
       </c>
@@ -32588,7 +32591,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="847" hidden="1" spans="1:9">
+    <row r="847" spans="1:9">
       <c r="A847" s="8">
         <v>9</v>
       </c>
@@ -32614,7 +32617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="848" hidden="1" spans="1:9">
+    <row r="848" spans="1:9">
       <c r="A848" s="8">
         <v>10</v>
       </c>
@@ -32640,7 +32643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="849" hidden="1" spans="1:9">
+    <row r="849" spans="1:9">
       <c r="A849" s="8">
         <v>11</v>
       </c>
@@ -32666,7 +32669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="850" hidden="1" spans="1:9">
+    <row r="850" spans="1:9">
       <c r="A850" s="8" t="s">
         <v>83</v>
       </c>
@@ -32692,7 +32695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="851" hidden="1" spans="1:9">
+    <row r="851" spans="1:9">
       <c r="A851" s="8">
         <v>1</v>
       </c>
@@ -32721,7 +32724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="852" hidden="1" spans="1:9">
+    <row r="852" spans="1:9">
       <c r="A852" s="8">
         <v>2</v>
       </c>
@@ -32750,7 +32753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="853" hidden="1" spans="1:9">
+    <row r="853" spans="1:9">
       <c r="A853" s="8">
         <v>3</v>
       </c>
@@ -32776,7 +32779,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="854" hidden="1" spans="1:9">
+    <row r="854" spans="1:9">
       <c r="A854" s="8">
         <v>4</v>
       </c>
@@ -32805,7 +32808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="855" hidden="1" spans="1:9">
+    <row r="855" spans="1:9">
       <c r="A855" s="8">
         <v>5</v>
       </c>
@@ -32831,7 +32834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="856" hidden="1" spans="1:9">
+    <row r="856" spans="1:9">
       <c r="A856" s="8">
         <v>6</v>
       </c>
@@ -32860,7 +32863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="857" hidden="1" spans="1:9">
+    <row r="857" spans="1:9">
       <c r="A857" s="8">
         <v>7</v>
       </c>
@@ -32889,7 +32892,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="858" hidden="1" spans="1:9">
+    <row r="858" spans="1:9">
       <c r="A858" s="8" t="s">
         <v>83</v>
       </c>
@@ -32915,236 +32918,237 @@
         <v>15</v>
       </c>
     </row>
-    <row r="859" hidden="1" spans="1:9">
-      <c r="A859" s="8">
+    <row r="859" s="7" customFormat="1" spans="1:9">
+      <c r="A859" s="18">
         <v>1</v>
       </c>
-      <c r="B859" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C859" s="8" t="s">
+      <c r="B859" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C859" s="18" t="s">
         <v>1532</v>
       </c>
-      <c r="D859" s="8" t="s">
+      <c r="D859" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E859" s="8" t="s">
+      <c r="E859" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="F859" s="26" t="s">
+        <v>1533</v>
+      </c>
+      <c r="G859" s="18">
+        <v>9</v>
+      </c>
+      <c r="H859" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I859" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="860" s="7" customFormat="1" spans="1:9">
+      <c r="A860" s="18">
+        <v>2</v>
+      </c>
+      <c r="B860" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C860" s="18" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D860" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E860" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F860" s="26" t="s">
+        <v>1534</v>
+      </c>
+      <c r="G860" s="18">
+        <v>7</v>
+      </c>
+      <c r="H860" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I860" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="861" s="7" customFormat="1" spans="1:9">
+      <c r="A861" s="18">
+        <v>3</v>
+      </c>
+      <c r="B861" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C861" s="18" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D861" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E861" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="F861" s="26" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G861" s="18">
+        <v>6</v>
+      </c>
+      <c r="H861" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I861" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="862" s="7" customFormat="1" spans="1:9">
+      <c r="A862" s="18">
+        <v>4</v>
+      </c>
+      <c r="B862" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C862" s="18" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D862" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E862" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F862" s="26" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G862" s="18">
+        <v>5</v>
+      </c>
+      <c r="H862" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I862" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="863" s="7" customFormat="1" spans="1:9">
+      <c r="A863" s="18">
+        <v>5</v>
+      </c>
+      <c r="B863" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C863" s="18" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D863" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E863" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F863" s="26" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G863" s="18">
+        <v>4</v>
+      </c>
+      <c r="H863" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I863" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="864" s="7" customFormat="1" spans="1:9">
+      <c r="A864" s="18">
+        <v>6</v>
+      </c>
+      <c r="B864" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C864" s="18" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D864" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E864" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="F864" s="26" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G864" s="18">
+        <v>3</v>
+      </c>
+      <c r="H864" s="6"/>
+      <c r="I864" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="865" s="7" customFormat="1" spans="1:9">
+      <c r="A865" s="18">
+        <v>7</v>
+      </c>
+      <c r="B865" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C865" s="18" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D865" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E865" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="F865" s="26" t="s">
+        <v>1539</v>
+      </c>
+      <c r="G865" s="18">
+        <v>2</v>
+      </c>
+      <c r="H865" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I865" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="866" s="7" customFormat="1" spans="1:9">
+      <c r="A866" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B866" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C866" s="18" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D866" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E866" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F859" s="24" t="s">
-        <v>1533</v>
-      </c>
-      <c r="G859" s="8">
-        <v>9</v>
-      </c>
-      <c r="H859" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="I859" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="860" hidden="1" spans="1:9">
-      <c r="A860" s="8">
-        <v>2</v>
-      </c>
-      <c r="B860" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C860" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D860" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E860" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="F860" s="24" t="s">
-        <v>1534</v>
-      </c>
-      <c r="G860" s="8">
-        <v>7</v>
-      </c>
-      <c r="H860" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="I860" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="861" hidden="1" spans="1:9">
-      <c r="A861" s="8">
-        <v>3</v>
-      </c>
-      <c r="B861" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C861" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D861" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E861" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F861" s="24" t="s">
-        <v>1535</v>
-      </c>
-      <c r="G861" s="8">
-        <v>6</v>
-      </c>
-      <c r="H861" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I861" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="862" hidden="1" spans="1:9">
-      <c r="A862" s="8">
-        <v>4</v>
-      </c>
-      <c r="B862" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C862" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D862" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E862" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="F862" s="24" t="s">
-        <v>1536</v>
-      </c>
-      <c r="G862" s="8">
-        <v>5</v>
-      </c>
-      <c r="H862" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I862" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="863" hidden="1" spans="1:9">
-      <c r="A863" s="8">
-        <v>5</v>
-      </c>
-      <c r="B863" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C863" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D863" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E863" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F863" s="24" t="s">
-        <v>1537</v>
-      </c>
-      <c r="G863" s="8">
-        <v>4</v>
-      </c>
-      <c r="H863" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I863" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="864" hidden="1" spans="1:9">
-      <c r="A864" s="8">
-        <v>6</v>
-      </c>
-      <c r="B864" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C864" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D864" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E864" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F864" s="24" t="s">
-        <v>1538</v>
-      </c>
-      <c r="G864" s="8">
-        <v>3</v>
-      </c>
-      <c r="I864" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="865" hidden="1" spans="1:9">
-      <c r="A865" s="8">
-        <v>7</v>
-      </c>
-      <c r="B865" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C865" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D865" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E865" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F865" s="24" t="s">
-        <v>1539</v>
-      </c>
-      <c r="G865" s="8">
-        <v>2</v>
-      </c>
-      <c r="H865" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I865" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="866" hidden="1" spans="1:9">
-      <c r="A866" s="8">
-        <v>8</v>
-      </c>
-      <c r="B866" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C866" s="8" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D866" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E866" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F866" s="24" t="s">
+      <c r="F866" s="26" t="s">
         <v>1540</v>
       </c>
-      <c r="G866" s="8">
-        <v>1</v>
-      </c>
-      <c r="H866" s="14" t="s">
+      <c r="G866" s="18">
+        <v>0</v>
+      </c>
+      <c r="H866" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I866" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="867" hidden="1" spans="1:9">
+      <c r="I866" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="867" spans="1:9">
       <c r="A867" s="8">
         <v>1</v>
       </c>
@@ -33173,7 +33177,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="868" hidden="1" spans="1:9">
+    <row r="868" spans="1:9">
       <c r="A868" s="8">
         <v>2</v>
       </c>
@@ -33202,7 +33206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="869" hidden="1" spans="1:9">
+    <row r="869" spans="1:9">
       <c r="A869" s="8">
         <v>3</v>
       </c>
@@ -33228,7 +33232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="870" hidden="1" spans="1:9">
+    <row r="870" spans="1:9">
       <c r="A870" s="8">
         <v>4</v>
       </c>
@@ -33254,7 +33258,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="871" hidden="1" spans="1:9">
+    <row r="871" spans="1:9">
       <c r="A871" s="8">
         <v>5</v>
       </c>
@@ -33280,7 +33284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="872" hidden="1" spans="1:9">
+    <row r="872" spans="1:9">
       <c r="A872" s="8">
         <v>6</v>
       </c>
@@ -33306,7 +33310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="873" hidden="1" spans="1:9">
+    <row r="873" spans="1:9">
       <c r="A873" s="8">
         <v>7</v>
       </c>
@@ -33332,7 +33336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="874" hidden="1" spans="1:9">
+    <row r="874" spans="1:9">
       <c r="A874" s="8">
         <v>8</v>
       </c>
@@ -34712,9 +34716,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I926" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="8">
-      <filters blank="1"/>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
